--- a/TrackModel/Green Line.xlsx
+++ b/TrackModel/Green Line.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pitt-my.sharepoint.com/personal/dgs44_pitt_edu/Documents/Trains/TrackModel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="534" documentId="8_{D0660D75-C052-4898-8402-12AA78E71664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7205EDC-4AF8-48D2-B023-53E69B9CFDD7}"/>
+  <xr:revisionPtr revIDLastSave="538" documentId="8_{D0660D75-C052-4898-8402-12AA78E71664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1693742A-DC0C-4460-90B3-D5A8C7F9DBD6}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{C71A2FFE-490E-4D57-BAA4-DE7AC575C897}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C71A2FFE-490E-4D57-BAA4-DE7AC575C897}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -817,7 +817,7 @@
         <v>1.6</v>
       </c>
       <c r="R4" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S4" s="3">
         <v>1</v>
@@ -1006,12 +1006,8 @@
       <c r="H9" s="2">
         <v>12</v>
       </c>
-      <c r="J9" s="2">
-        <v>6</v>
-      </c>
-      <c r="K9" s="2">
-        <v>12</v>
-      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
       <c r="P9" s="3">
         <v>16</v>
       </c>
@@ -1245,12 +1241,6 @@
       <c r="H15" s="2">
         <v>0.5</v>
       </c>
-      <c r="J15" s="3">
-        <v>1</v>
-      </c>
-      <c r="K15" s="3">
-        <v>13</v>
-      </c>
       <c r="P15" s="3">
         <v>11</v>
       </c>
@@ -1290,6 +1280,12 @@
       </c>
       <c r="H16" s="2">
         <v>0.5</v>
+      </c>
+      <c r="J16" s="3">
+        <v>1</v>
+      </c>
+      <c r="K16" s="3">
+        <v>12</v>
       </c>
       <c r="P16" s="3">
         <v>10</v>

--- a/TrackModel/Green Line.xlsx
+++ b/TrackModel/Green Line.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pitt-my.sharepoint.com/personal/dgs44_pitt_edu/Documents/Trains/TrackModel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="538" documentId="8_{D0660D75-C052-4898-8402-12AA78E71664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1693742A-DC0C-4460-90B3-D5A8C7F9DBD6}"/>
+  <xr:revisionPtr revIDLastSave="568" documentId="8_{D0660D75-C052-4898-8402-12AA78E71664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8C98194-8817-4F58-A7F3-D176B0B28C60}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C71A2FFE-490E-4D57-BAA4-DE7AC575C897}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="62">
   <si>
     <t>A</t>
   </si>
@@ -216,6 +216,12 @@
   </si>
   <si>
     <t>Yard</t>
+  </si>
+  <si>
+    <t>adj1</t>
+  </si>
+  <si>
+    <t>adj2</t>
   </si>
 </sst>
 </file>
@@ -614,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13190075-78CA-4D81-A78A-8327AF8C2968}">
-  <dimension ref="A1:S156"/>
+  <dimension ref="A1:U156"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="11" width="9.140625" style="3"/>
@@ -624,7 +630,7 @@
     <col min="16" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="3">
         <v>0</v>
       </c>
@@ -682,8 +688,14 @@
       <c r="S1" s="3">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T1" s="3">
+        <v>19</v>
+      </c>
+      <c r="U1" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -741,8 +753,14 @@
       <c r="S2" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -786,8 +804,14 @@
       <c r="S3" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T3" s="3">
+        <v>58</v>
+      </c>
+      <c r="U3" s="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -822,8 +846,14 @@
       <c r="S4" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T4" s="3">
+        <v>13</v>
+      </c>
+      <c r="U4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
@@ -860,8 +890,14 @@
         <f t="shared" si="0"/>
         <v>1.6</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T5" s="3">
+        <v>1</v>
+      </c>
+      <c r="U5" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -904,8 +940,14 @@
         <f t="shared" si="0"/>
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T6" s="3">
+        <v>2</v>
+      </c>
+      <c r="U6" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -942,8 +984,14 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T7" s="3">
+        <v>3</v>
+      </c>
+      <c r="U7" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
@@ -982,8 +1030,14 @@
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T8" s="3">
+        <v>4</v>
+      </c>
+      <c r="U8" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -1022,8 +1076,14 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T9" s="3">
+        <v>5</v>
+      </c>
+      <c r="U9" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
@@ -1060,8 +1120,14 @@
         <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T10" s="3">
+        <v>6</v>
+      </c>
+      <c r="U10" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -1098,8 +1164,14 @@
         <f t="shared" ref="S11:S31" si="2">Q10</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T11" s="3">
+        <v>7</v>
+      </c>
+      <c r="U11" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -1142,8 +1214,14 @@
         <f t="shared" ref="S12:S16" si="4">Q11</f>
         <v>2.5</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T12" s="3">
+        <v>8</v>
+      </c>
+      <c r="U12" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -1180,8 +1258,14 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T13" s="3">
+        <v>9</v>
+      </c>
+      <c r="U13" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -1218,8 +1302,14 @@
         <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T14" s="3">
+        <v>10</v>
+      </c>
+      <c r="U14" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
@@ -1255,8 +1345,14 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T15" s="3">
+        <v>11</v>
+      </c>
+      <c r="U15" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
@@ -1301,8 +1397,14 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T16" s="3">
+        <v>12</v>
+      </c>
+      <c r="U16" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
@@ -1341,8 +1443,14 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T17" s="3">
+        <v>13</v>
+      </c>
+      <c r="U17" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
@@ -1381,8 +1489,14 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T18" s="3">
+        <v>14</v>
+      </c>
+      <c r="U18" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>20</v>
       </c>
@@ -1427,8 +1541,14 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T19" s="3">
+        <v>15</v>
+      </c>
+      <c r="U19" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
@@ -1467,8 +1587,14 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T20" s="3">
+        <v>16</v>
+      </c>
+      <c r="U20" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -1507,8 +1633,14 @@
         <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
-    </row>
-    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T21" s="3">
+        <v>17</v>
+      </c>
+      <c r="U21" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
@@ -1550,8 +1682,14 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T22" s="3">
+        <v>18</v>
+      </c>
+      <c r="U22" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
@@ -1590,8 +1728,14 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T23" s="3">
+        <v>19</v>
+      </c>
+      <c r="U23" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
@@ -1632,8 +1776,14 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T24" s="3">
+        <v>20</v>
+      </c>
+      <c r="U24" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>20</v>
       </c>
@@ -1680,8 +1830,14 @@
         <f t="shared" si="2"/>
         <v>4.5999999999999996</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T25" s="3">
+        <v>21</v>
+      </c>
+      <c r="U25" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>20</v>
       </c>
@@ -1722,8 +1878,14 @@
         <f t="shared" si="2"/>
         <v>5.1999999999999993</v>
       </c>
-    </row>
-    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T26" s="3">
+        <v>22</v>
+      </c>
+      <c r="U26" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>20</v>
       </c>
@@ -1764,8 +1926,14 @@
         <f t="shared" si="2"/>
         <v>5.7999999999999989</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T27" s="3">
+        <v>23</v>
+      </c>
+      <c r="U27" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>20</v>
       </c>
@@ -1806,8 +1974,14 @@
         <f t="shared" si="2"/>
         <v>6.3999999999999986</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T28" s="3">
+        <v>24</v>
+      </c>
+      <c r="U28" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>20</v>
       </c>
@@ -1848,8 +2022,14 @@
         <f t="shared" si="2"/>
         <v>6.9999999999999982</v>
       </c>
-    </row>
-    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T29" s="3">
+        <v>25</v>
+      </c>
+      <c r="U29" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>20</v>
       </c>
@@ -1890,8 +2070,14 @@
         <f t="shared" si="2"/>
         <v>7.5999999999999979</v>
       </c>
-    </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T30" s="3">
+        <v>26</v>
+      </c>
+      <c r="U30" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>20</v>
       </c>
@@ -1938,8 +2124,14 @@
         <f t="shared" si="2"/>
         <v>8.1999999999999975</v>
       </c>
-    </row>
-    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T31" s="3">
+        <v>27</v>
+      </c>
+      <c r="U31" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>20</v>
       </c>
@@ -1977,8 +2169,14 @@
         <f>Q31+0.6</f>
         <v>9.3999999999999968</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T32" s="3">
+        <v>28</v>
+      </c>
+      <c r="U32" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>20</v>
       </c>
@@ -2016,8 +2214,14 @@
         <f t="shared" ref="S33:S35" si="10">S32+0.6</f>
         <v>9.9999999999999964</v>
       </c>
-    </row>
-    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T33" s="3">
+        <v>29</v>
+      </c>
+      <c r="U33" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>20</v>
       </c>
@@ -2061,8 +2265,14 @@
         <f t="shared" si="10"/>
         <v>10.599999999999996</v>
       </c>
-    </row>
-    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T34" s="3">
+        <v>30</v>
+      </c>
+      <c r="U34" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>20</v>
       </c>
@@ -2100,8 +2310,14 @@
         <f t="shared" si="10"/>
         <v>11.199999999999996</v>
       </c>
-    </row>
-    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T35" s="3">
+        <v>31</v>
+      </c>
+      <c r="U35" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>20</v>
       </c>
@@ -2139,8 +2355,14 @@
         <f>S35+0.8</f>
         <v>11.999999999999996</v>
       </c>
-    </row>
-    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T36" s="3">
+        <v>32</v>
+      </c>
+      <c r="U36" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>20</v>
       </c>
@@ -2178,8 +2400,14 @@
         <f t="shared" ref="S37:S38" si="12">S36+0.8</f>
         <v>12.799999999999997</v>
       </c>
-    </row>
-    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T37" s="3">
+        <v>33</v>
+      </c>
+      <c r="U37" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>20</v>
       </c>
@@ -2217,8 +2445,14 @@
         <f t="shared" si="12"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T38" s="3">
+        <v>34</v>
+      </c>
+      <c r="U38" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>20</v>
       </c>
@@ -2259,8 +2493,14 @@
         <f>S38</f>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T39" s="3">
+        <v>35</v>
+      </c>
+      <c r="U39" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>20</v>
       </c>
@@ -2301,8 +2541,14 @@
         <f t="shared" ref="S40:S60" si="14">S39</f>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T40" s="3">
+        <v>36</v>
+      </c>
+      <c r="U40" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>20</v>
       </c>
@@ -2343,8 +2589,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T41" s="3">
+        <v>37</v>
+      </c>
+      <c r="U41" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>20</v>
       </c>
@@ -2391,8 +2643,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T42" s="3">
+        <v>38</v>
+      </c>
+      <c r="U42" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>20</v>
       </c>
@@ -2433,8 +2691,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T43" s="3">
+        <v>39</v>
+      </c>
+      <c r="U43" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>20</v>
       </c>
@@ -2475,8 +2739,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T44" s="3">
+        <v>40</v>
+      </c>
+      <c r="U44" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>20</v>
       </c>
@@ -2517,8 +2787,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T45" s="3">
+        <v>41</v>
+      </c>
+      <c r="U45" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>20</v>
       </c>
@@ -2559,8 +2835,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T46" s="3">
+        <v>42</v>
+      </c>
+      <c r="U46" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>20</v>
       </c>
@@ -2601,8 +2883,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T47" s="3">
+        <v>43</v>
+      </c>
+      <c r="U47" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>20</v>
       </c>
@@ -2643,8 +2931,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T48" s="3">
+        <v>44</v>
+      </c>
+      <c r="U48" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>20</v>
       </c>
@@ -2685,8 +2979,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T49" s="3">
+        <v>45</v>
+      </c>
+      <c r="U49" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>20</v>
       </c>
@@ -2727,8 +3027,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T50" s="3">
+        <v>46</v>
+      </c>
+      <c r="U50" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>20</v>
       </c>
@@ -2775,8 +3081,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T51" s="3">
+        <v>47</v>
+      </c>
+      <c r="U51" s="3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>20</v>
       </c>
@@ -2817,8 +3129,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T52" s="3">
+        <v>48</v>
+      </c>
+      <c r="U52" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>20</v>
       </c>
@@ -2859,8 +3177,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T53" s="3">
+        <v>49</v>
+      </c>
+      <c r="U53" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>20</v>
       </c>
@@ -2901,8 +3225,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T54" s="3">
+        <v>50</v>
+      </c>
+      <c r="U54" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>20</v>
       </c>
@@ -2943,8 +3273,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T55" s="3">
+        <v>51</v>
+      </c>
+      <c r="U55" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>20</v>
       </c>
@@ -2985,8 +3321,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T56" s="3">
+        <v>52</v>
+      </c>
+      <c r="U56" s="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>20</v>
       </c>
@@ -3027,8 +3369,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T57" s="3">
+        <v>53</v>
+      </c>
+      <c r="U57" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>20</v>
       </c>
@@ -3069,8 +3417,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T58" s="3">
+        <v>54</v>
+      </c>
+      <c r="U58" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>20</v>
       </c>
@@ -3111,8 +3465,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T59" s="3">
+        <v>55</v>
+      </c>
+      <c r="U59" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>20</v>
       </c>
@@ -3159,8 +3519,14 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-    </row>
-    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T60" s="3">
+        <v>56</v>
+      </c>
+      <c r="U60" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>20</v>
       </c>
@@ -3204,8 +3570,14 @@
         <f>S60+0.8</f>
         <v>14.399999999999999</v>
       </c>
-    </row>
-    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T61" s="3">
+        <v>57</v>
+      </c>
+      <c r="U61" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>20</v>
       </c>
@@ -3243,8 +3615,14 @@
         <f t="shared" ref="S62:S65" si="18">S61+0.8</f>
         <v>15.2</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T62" s="3">
+        <v>58</v>
+      </c>
+      <c r="U62" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>20</v>
       </c>
@@ -3282,8 +3660,14 @@
         <f t="shared" si="18"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T63" s="3">
+        <v>59</v>
+      </c>
+      <c r="U63" s="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>20</v>
       </c>
@@ -3321,8 +3705,14 @@
         <f t="shared" si="18"/>
         <v>16.8</v>
       </c>
-    </row>
-    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T64" s="3">
+        <v>60</v>
+      </c>
+      <c r="U64" s="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>20</v>
       </c>
@@ -3366,8 +3756,14 @@
         <f t="shared" si="18"/>
         <v>17.600000000000001</v>
       </c>
-    </row>
-    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T65" s="3">
+        <v>61</v>
+      </c>
+      <c r="U65" s="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>20</v>
       </c>
@@ -3405,8 +3801,14 @@
         <f>S65+1</f>
         <v>18.600000000000001</v>
       </c>
-    </row>
-    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T66" s="3">
+        <v>62</v>
+      </c>
+      <c r="U66" s="3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>20</v>
       </c>
@@ -3444,8 +3846,14 @@
         <f>S66+1</f>
         <v>19.600000000000001</v>
       </c>
-    </row>
-    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T67" s="3">
+        <v>63</v>
+      </c>
+      <c r="U67" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>20</v>
       </c>
@@ -3489,8 +3897,14 @@
         <f>S65+4.2</f>
         <v>21.8</v>
       </c>
-    </row>
-    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T68" s="3">
+        <v>64</v>
+      </c>
+      <c r="U68" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>20</v>
       </c>
@@ -3528,8 +3942,14 @@
         <f>S68+2.2</f>
         <v>24</v>
       </c>
-    </row>
-    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T69" s="3">
+        <v>65</v>
+      </c>
+      <c r="U69" s="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>20</v>
       </c>
@@ -3567,8 +3987,14 @@
         <f>S69+1</f>
         <v>25</v>
       </c>
-    </row>
-    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T70" s="3">
+        <v>66</v>
+      </c>
+      <c r="U70" s="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>20</v>
       </c>
@@ -3606,8 +4032,14 @@
         <f>S68+4.2</f>
         <v>26</v>
       </c>
-    </row>
-    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T71" s="3">
+        <v>67</v>
+      </c>
+      <c r="U71" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>20</v>
       </c>
@@ -3645,8 +4077,14 @@
         <f>S71+1</f>
         <v>27</v>
       </c>
-    </row>
-    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T72" s="3">
+        <v>68</v>
+      </c>
+      <c r="U72" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>20</v>
       </c>
@@ -3684,8 +4122,14 @@
         <f t="shared" ref="S73:S76" si="23">S72+1</f>
         <v>28</v>
       </c>
-    </row>
-    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T73" s="3">
+        <v>69</v>
+      </c>
+      <c r="U73" s="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>20</v>
       </c>
@@ -3723,8 +4167,14 @@
         <f t="shared" si="23"/>
         <v>29</v>
       </c>
-    </row>
-    <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T74" s="3">
+        <v>70</v>
+      </c>
+      <c r="U74" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>20</v>
       </c>
@@ -3762,8 +4212,14 @@
         <f t="shared" si="23"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T75" s="3">
+        <v>71</v>
+      </c>
+      <c r="U75" s="3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>20</v>
       </c>
@@ -3807,8 +4263,14 @@
         <f t="shared" si="23"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="77" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T76" s="3">
+        <v>72</v>
+      </c>
+      <c r="U76" s="3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>20</v>
       </c>
@@ -3849,8 +4311,14 @@
         <f>S76</f>
         <v>31</v>
       </c>
-    </row>
-    <row r="78" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T77" s="3">
+        <v>73</v>
+      </c>
+      <c r="U77" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>20</v>
       </c>
@@ -3891,8 +4359,14 @@
         <f t="shared" ref="S78:S79" si="25">S77</f>
         <v>31</v>
       </c>
-    </row>
-    <row r="79" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T78" s="3">
+        <v>74</v>
+      </c>
+      <c r="U78" s="3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>20</v>
       </c>
@@ -3916,12 +4390,6 @@
       </c>
       <c r="H79" s="2">
         <v>0.5</v>
-      </c>
-      <c r="J79" s="3">
-        <v>77</v>
-      </c>
-      <c r="K79" s="3">
-        <v>101</v>
       </c>
       <c r="P79" s="3">
         <f t="shared" si="19"/>
@@ -3939,8 +4407,14 @@
         <f t="shared" si="25"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="80" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T79" s="3">
+        <v>75</v>
+      </c>
+      <c r="U79" s="3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>20</v>
       </c>
@@ -3964,6 +4438,12 @@
       </c>
       <c r="H80" s="2">
         <v>0.5</v>
+      </c>
+      <c r="J80" s="3">
+        <v>76</v>
+      </c>
+      <c r="K80" s="3">
+        <v>101</v>
       </c>
       <c r="M80" s="3" t="s">
         <v>52</v>
@@ -3987,8 +4467,14 @@
         <f>S79</f>
         <v>31</v>
       </c>
-    </row>
-    <row r="81" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T80" s="3">
+        <v>76</v>
+      </c>
+      <c r="U80" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>20</v>
       </c>
@@ -4029,8 +4515,14 @@
         <f t="shared" ref="S81:S88" si="27">S80</f>
         <v>31</v>
       </c>
-    </row>
-    <row r="82" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T81" s="3">
+        <v>77</v>
+      </c>
+      <c r="U81" s="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>20</v>
       </c>
@@ -4071,8 +4563,14 @@
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="83" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T82" s="3">
+        <v>78</v>
+      </c>
+      <c r="U82" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>20</v>
       </c>
@@ -4113,8 +4611,14 @@
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="84" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T83" s="3">
+        <v>79</v>
+      </c>
+      <c r="U83" s="3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>20</v>
       </c>
@@ -4155,8 +4659,14 @@
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="85" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T84" s="3">
+        <v>80</v>
+      </c>
+      <c r="U84" s="3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>20</v>
       </c>
@@ -4197,8 +4707,14 @@
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="86" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T85" s="3">
+        <v>81</v>
+      </c>
+      <c r="U85" s="3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>20</v>
       </c>
@@ -4239,8 +4755,14 @@
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="87" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T86" s="3">
+        <v>82</v>
+      </c>
+      <c r="U86" s="3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>20</v>
       </c>
@@ -4281,8 +4803,14 @@
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="88" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T87" s="3">
+        <v>83</v>
+      </c>
+      <c r="U87" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>20</v>
       </c>
@@ -4329,8 +4857,14 @@
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="89" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T88" s="3">
+        <v>84</v>
+      </c>
+      <c r="U88" s="3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>20</v>
       </c>
@@ -4371,8 +4905,14 @@
         <f>S88</f>
         <v>31</v>
       </c>
-    </row>
-    <row r="90" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T89" s="3">
+        <v>85</v>
+      </c>
+      <c r="U89" s="3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>20</v>
       </c>
@@ -4413,8 +4953,14 @@
         <f t="shared" ref="S90:S91" si="29">S89</f>
         <v>31</v>
       </c>
-    </row>
-    <row r="91" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T90" s="3">
+        <v>86</v>
+      </c>
+      <c r="U90" s="3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>20</v>
       </c>
@@ -4461,8 +5007,14 @@
         <f t="shared" si="29"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="92" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T91" s="3">
+        <v>87</v>
+      </c>
+      <c r="U91" s="3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>20</v>
       </c>
@@ -4500,8 +5052,14 @@
         <f>S91-0.8</f>
         <v>30.2</v>
       </c>
-    </row>
-    <row r="93" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T92" s="3">
+        <v>88</v>
+      </c>
+      <c r="U92" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>20</v>
       </c>
@@ -4539,8 +5097,14 @@
         <f t="shared" ref="S93:S97" si="31">S92-0.8</f>
         <v>29.4</v>
       </c>
-    </row>
-    <row r="94" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T93" s="3">
+        <v>89</v>
+      </c>
+      <c r="U93" s="3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>20</v>
       </c>
@@ -4578,8 +5142,14 @@
         <f t="shared" si="31"/>
         <v>28.599999999999998</v>
       </c>
-    </row>
-    <row r="95" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T94" s="3">
+        <v>90</v>
+      </c>
+      <c r="U94" s="3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>20</v>
       </c>
@@ -4617,8 +5187,14 @@
         <f t="shared" si="31"/>
         <v>27.799999999999997</v>
       </c>
-    </row>
-    <row r="96" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T95" s="3">
+        <v>91</v>
+      </c>
+      <c r="U95" s="3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>20</v>
       </c>
@@ -4656,8 +5232,14 @@
         <f t="shared" si="31"/>
         <v>26.999999999999996</v>
       </c>
-    </row>
-    <row r="97" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T96" s="3">
+        <v>92</v>
+      </c>
+      <c r="U96" s="3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>20</v>
       </c>
@@ -4695,8 +5277,14 @@
         <f t="shared" si="31"/>
         <v>26.199999999999996</v>
       </c>
-    </row>
-    <row r="98" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T97" s="3">
+        <v>93</v>
+      </c>
+      <c r="U97" s="3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>20</v>
       </c>
@@ -4734,8 +5322,14 @@
         <f>S97+0.8</f>
         <v>26.999999999999996</v>
       </c>
-    </row>
-    <row r="99" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T98" s="3">
+        <v>94</v>
+      </c>
+      <c r="U98" s="3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>20</v>
       </c>
@@ -4779,8 +5373,14 @@
         <f t="shared" ref="S99:S100" si="33">S98+0.8</f>
         <v>27.799999999999997</v>
       </c>
-    </row>
-    <row r="100" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T99" s="3">
+        <v>95</v>
+      </c>
+      <c r="U99" s="3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>20</v>
       </c>
@@ -4818,8 +5418,14 @@
         <f t="shared" si="33"/>
         <v>28.599999999999998</v>
       </c>
-    </row>
-    <row r="101" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T100" s="3">
+        <v>96</v>
+      </c>
+      <c r="U100" s="3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>20</v>
       </c>
@@ -4857,8 +5463,14 @@
         <f>S100+0.8</f>
         <v>29.4</v>
       </c>
-    </row>
-    <row r="102" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T101" s="3">
+        <v>97</v>
+      </c>
+      <c r="U101" s="3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>20</v>
       </c>
@@ -4896,8 +5508,14 @@
         <f t="shared" ref="S102:S103" si="35">S101+0.8</f>
         <v>30.2</v>
       </c>
-    </row>
-    <row r="103" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T102" s="3">
+        <v>98</v>
+      </c>
+      <c r="U102" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>20</v>
       </c>
@@ -4935,8 +5553,14 @@
         <f t="shared" si="35"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="104" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T103" s="3">
+        <v>99</v>
+      </c>
+      <c r="U103" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>20</v>
       </c>
@@ -4970,8 +5594,14 @@
       <c r="S104" s="3">
         <v>29</v>
       </c>
-    </row>
-    <row r="105" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T104" s="3">
+        <v>77</v>
+      </c>
+      <c r="U104" s="3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>20</v>
       </c>
@@ -5007,8 +5637,14 @@
       <c r="S105" s="3">
         <v>29</v>
       </c>
-    </row>
-    <row r="106" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T105" s="3">
+        <v>101</v>
+      </c>
+      <c r="U105" s="3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>20</v>
       </c>
@@ -5044,8 +5680,14 @@
       <c r="S106" s="3">
         <v>29</v>
       </c>
-    </row>
-    <row r="107" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T106" s="3">
+        <v>102</v>
+      </c>
+      <c r="U106" s="3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>20</v>
       </c>
@@ -5081,8 +5723,14 @@
       <c r="S107" s="3">
         <v>29</v>
       </c>
-    </row>
-    <row r="108" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T107" s="3">
+        <v>103</v>
+      </c>
+      <c r="U107" s="3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>20</v>
       </c>
@@ -5126,8 +5774,14 @@
         <f>S107-1</f>
         <v>28</v>
       </c>
-    </row>
-    <row r="109" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T108" s="3">
+        <v>104</v>
+      </c>
+      <c r="U108" s="3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>20</v>
       </c>
@@ -5165,8 +5819,14 @@
         <f t="shared" ref="S109:S112" si="37">S108-1</f>
         <v>27</v>
       </c>
-    </row>
-    <row r="110" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T109" s="3">
+        <v>105</v>
+      </c>
+      <c r="U109" s="3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>20</v>
       </c>
@@ -5204,8 +5864,14 @@
         <f t="shared" si="37"/>
         <v>26</v>
       </c>
-    </row>
-    <row r="111" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T110" s="3">
+        <v>106</v>
+      </c>
+      <c r="U110" s="3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>20</v>
       </c>
@@ -5246,8 +5912,14 @@
         <f t="shared" si="37"/>
         <v>25</v>
       </c>
-    </row>
-    <row r="112" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T111" s="3">
+        <v>107</v>
+      </c>
+      <c r="U111" s="3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>20</v>
       </c>
@@ -5285,8 +5957,14 @@
         <f t="shared" si="37"/>
         <v>24</v>
       </c>
-    </row>
-    <row r="113" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T112" s="3">
+        <v>108</v>
+      </c>
+      <c r="U112" s="3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>20</v>
       </c>
@@ -5324,8 +6002,14 @@
         <f>S112-0.7</f>
         <v>23.3</v>
       </c>
-    </row>
-    <row r="114" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T113" s="3">
+        <v>109</v>
+      </c>
+      <c r="U113" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>20</v>
       </c>
@@ -5363,8 +6047,14 @@
         <f t="shared" ref="S114:S119" si="39">S113-0.7</f>
         <v>22.6</v>
       </c>
-    </row>
-    <row r="115" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T114" s="3">
+        <v>110</v>
+      </c>
+      <c r="U114" s="3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>20</v>
       </c>
@@ -5402,8 +6092,14 @@
         <f t="shared" si="39"/>
         <v>21.900000000000002</v>
       </c>
-    </row>
-    <row r="116" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T115" s="3">
+        <v>111</v>
+      </c>
+      <c r="U115" s="3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>20</v>
       </c>
@@ -5441,8 +6137,14 @@
         <f t="shared" si="39"/>
         <v>21.200000000000003</v>
       </c>
-    </row>
-    <row r="117" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T116" s="3">
+        <v>112</v>
+      </c>
+      <c r="U116" s="3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>20</v>
       </c>
@@ -5486,8 +6188,14 @@
         <f t="shared" si="39"/>
         <v>20.500000000000004</v>
       </c>
-    </row>
-    <row r="118" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T117" s="3">
+        <v>113</v>
+      </c>
+      <c r="U117" s="3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>20</v>
       </c>
@@ -5525,8 +6233,14 @@
         <f t="shared" si="39"/>
         <v>19.800000000000004</v>
       </c>
-    </row>
-    <row r="119" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T118" s="3">
+        <v>114</v>
+      </c>
+      <c r="U118" s="3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>20</v>
       </c>
@@ -5564,8 +6278,14 @@
         <f t="shared" si="39"/>
         <v>19.100000000000005</v>
       </c>
-    </row>
-    <row r="120" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T119" s="3">
+        <v>115</v>
+      </c>
+      <c r="U119" s="3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>20</v>
       </c>
@@ -5603,8 +6323,14 @@
         <f>S119-0.8</f>
         <v>18.300000000000004</v>
       </c>
-    </row>
-    <row r="121" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T120" s="3">
+        <v>116</v>
+      </c>
+      <c r="U120" s="3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>20</v>
       </c>
@@ -5642,8 +6368,14 @@
         <f t="shared" ref="S121:S124" si="40">S120-0.8</f>
         <v>17.500000000000004</v>
       </c>
-    </row>
-    <row r="122" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T121" s="3">
+        <v>117</v>
+      </c>
+      <c r="U121" s="3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>20</v>
       </c>
@@ -5681,8 +6413,14 @@
         <f t="shared" si="40"/>
         <v>16.700000000000003</v>
       </c>
-    </row>
-    <row r="123" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T122" s="3">
+        <v>118</v>
+      </c>
+      <c r="U122" s="3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>20</v>
       </c>
@@ -5720,8 +6458,14 @@
         <f t="shared" si="40"/>
         <v>15.900000000000002</v>
       </c>
-    </row>
-    <row r="124" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T123" s="3">
+        <v>119</v>
+      </c>
+      <c r="U123" s="3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>20</v>
       </c>
@@ -5759,8 +6503,14 @@
         <f t="shared" si="40"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="125" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T124" s="3">
+        <v>120</v>
+      </c>
+      <c r="U124" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>20</v>
       </c>
@@ -5801,8 +6551,14 @@
         <f>S124</f>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="126" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T125" s="3">
+        <v>121</v>
+      </c>
+      <c r="U125" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>20</v>
       </c>
@@ -5849,8 +6605,14 @@
         <f t="shared" ref="S126:S146" si="43">S125</f>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="127" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T126" s="3">
+        <v>122</v>
+      </c>
+      <c r="U126" s="3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>20</v>
       </c>
@@ -5891,8 +6653,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="128" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T127" s="3">
+        <v>123</v>
+      </c>
+      <c r="U127" s="3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>20</v>
       </c>
@@ -5933,8 +6701,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="129" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T128" s="3">
+        <v>124</v>
+      </c>
+      <c r="U128" s="3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>20</v>
       </c>
@@ -5975,8 +6749,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="130" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T129" s="3">
+        <v>125</v>
+      </c>
+      <c r="U129" s="3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>20</v>
       </c>
@@ -6017,8 +6797,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="131" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T130" s="3">
+        <v>126</v>
+      </c>
+      <c r="U130" s="3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>20</v>
       </c>
@@ -6059,8 +6845,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="132" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T131" s="3">
+        <v>127</v>
+      </c>
+      <c r="U131" s="3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>20</v>
       </c>
@@ -6101,8 +6893,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="133" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T132" s="3">
+        <v>128</v>
+      </c>
+      <c r="U132" s="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>20</v>
       </c>
@@ -6143,8 +6941,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="134" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T133" s="3">
+        <v>129</v>
+      </c>
+      <c r="U133" s="3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>20</v>
       </c>
@@ -6185,8 +6989,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="135" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T134" s="3">
+        <v>130</v>
+      </c>
+      <c r="U134" s="3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>20</v>
       </c>
@@ -6233,8 +7043,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="136" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T135" s="3">
+        <v>131</v>
+      </c>
+      <c r="U135" s="3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>20</v>
       </c>
@@ -6275,8 +7091,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="137" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T136" s="3">
+        <v>132</v>
+      </c>
+      <c r="U136" s="3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>20</v>
       </c>
@@ -6317,8 +7139,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="138" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T137" s="3">
+        <v>133</v>
+      </c>
+      <c r="U137" s="3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>20</v>
       </c>
@@ -6359,8 +7187,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="139" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T138" s="3">
+        <v>134</v>
+      </c>
+      <c r="U138" s="3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>20</v>
       </c>
@@ -6401,8 +7235,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="140" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T139" s="3">
+        <v>135</v>
+      </c>
+      <c r="U139" s="3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="140" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>20</v>
       </c>
@@ -6443,8 +7283,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="141" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T140" s="3">
+        <v>136</v>
+      </c>
+      <c r="U140" s="3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="141" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>20</v>
       </c>
@@ -6485,8 +7331,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="142" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T141" s="3">
+        <v>137</v>
+      </c>
+      <c r="U141" s="3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="142" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>20</v>
       </c>
@@ -6527,8 +7379,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="143" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T142" s="3">
+        <v>138</v>
+      </c>
+      <c r="U142" s="3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="143" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>20</v>
       </c>
@@ -6569,8 +7427,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="144" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T143" s="3">
+        <v>139</v>
+      </c>
+      <c r="U143" s="3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>20</v>
       </c>
@@ -6617,8 +7481,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="145" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T144" s="3">
+        <v>140</v>
+      </c>
+      <c r="U144" s="3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>20</v>
       </c>
@@ -6659,8 +7529,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="146" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T145" s="3">
+        <v>141</v>
+      </c>
+      <c r="U145" s="3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="146" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>20</v>
       </c>
@@ -6701,8 +7577,14 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="147" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T146" s="3">
+        <v>142</v>
+      </c>
+      <c r="U146" s="3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="147" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>20</v>
       </c>
@@ -6740,8 +7622,14 @@
         <f>S146-0.7</f>
         <v>14.400000000000002</v>
       </c>
-    </row>
-    <row r="148" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T147" s="3">
+        <v>143</v>
+      </c>
+      <c r="U147" s="3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="148" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>20</v>
       </c>
@@ -6779,8 +7667,14 @@
         <f t="shared" ref="S148:S149" si="47">S147-0.7</f>
         <v>13.700000000000003</v>
       </c>
-    </row>
-    <row r="149" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T148" s="3">
+        <v>144</v>
+      </c>
+      <c r="U148" s="3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="149" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>20</v>
       </c>
@@ -6818,8 +7712,14 @@
         <f t="shared" si="47"/>
         <v>13.000000000000004</v>
       </c>
-    </row>
-    <row r="150" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T149" s="3">
+        <v>145</v>
+      </c>
+      <c r="U149" s="3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="150" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>20</v>
       </c>
@@ -6857,8 +7757,14 @@
         <f>S149-0.8</f>
         <v>12.200000000000003</v>
       </c>
-    </row>
-    <row r="151" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T150" s="3">
+        <v>146</v>
+      </c>
+      <c r="U150" s="3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="151" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>20</v>
       </c>
@@ -6896,8 +7802,14 @@
         <f t="shared" ref="S151:S152" si="49">S150-0.8</f>
         <v>11.400000000000002</v>
       </c>
-    </row>
-    <row r="152" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T151" s="3">
+        <v>147</v>
+      </c>
+      <c r="U151" s="3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="152" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>20</v>
       </c>
@@ -6935,8 +7847,14 @@
         <f t="shared" si="49"/>
         <v>10.600000000000001</v>
       </c>
-    </row>
-    <row r="153" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T152" s="3">
+        <v>148</v>
+      </c>
+      <c r="U152" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="153" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>20</v>
       </c>
@@ -6972,11 +7890,17 @@
       <c r="S153" s="3">
         <v>8.8000000000000007</v>
       </c>
-    </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T153" s="3">
+        <v>149</v>
+      </c>
+      <c r="U153" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="H155"/>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="H156"/>
     </row>
   </sheetData>

--- a/TrackModel/Green Line.xlsx
+++ b/TrackModel/Green Line.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pitt-my.sharepoint.com/personal/dgs44_pitt_edu/Documents/Trains/TrackModel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="568" documentId="8_{D0660D75-C052-4898-8402-12AA78E71664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8C98194-8817-4F58-A7F3-D176B0B28C60}"/>
+  <xr:revisionPtr revIDLastSave="608" documentId="8_{D0660D75-C052-4898-8402-12AA78E71664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50BA1C67-8B17-4746-87A0-AC8F3AF98ADC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C71A2FFE-490E-4D57-BAA4-DE7AC575C897}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="73">
   <si>
     <t>A</t>
   </si>
@@ -218,10 +218,43 @@
     <t>Yard</t>
   </si>
   <si>
-    <t>adj1</t>
-  </si>
-  <si>
-    <t>adj2</t>
+    <t>Edgebrook,L</t>
+  </si>
+  <si>
+    <t>Whited,LR</t>
+  </si>
+  <si>
+    <t>Station,LR</t>
+  </si>
+  <si>
+    <t>South Bank,L</t>
+  </si>
+  <si>
+    <t>Central,R</t>
+  </si>
+  <si>
+    <t>Inglewood,R</t>
+  </si>
+  <si>
+    <t>Overbrook,R</t>
+  </si>
+  <si>
+    <t>Glenbury,R</t>
+  </si>
+  <si>
+    <t>Dormont,R</t>
+  </si>
+  <si>
+    <t>Mt Lebanon,LR</t>
+  </si>
+  <si>
+    <t>Poplar,L</t>
+  </si>
+  <si>
+    <t>Castle Shannon,L</t>
+  </si>
+  <si>
+    <t>Inglewood,L</t>
   </si>
 </sst>
 </file>
@@ -688,12 +721,6 @@
       <c r="S1" s="3">
         <v>18</v>
       </c>
-      <c r="T1" s="3">
-        <v>19</v>
-      </c>
-      <c r="U1" s="3">
-        <v>20</v>
-      </c>
     </row>
     <row r="2" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -752,12 +779,6 @@
       </c>
       <c r="S2" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:21" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -804,12 +825,8 @@
       <c r="S3" s="3">
         <v>11</v>
       </c>
-      <c r="T3" s="3">
-        <v>58</v>
-      </c>
-      <c r="U3" s="3">
-        <v>62</v>
-      </c>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
     </row>
     <row r="4" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -845,12 +862,6 @@
       </c>
       <c r="S4" s="3">
         <v>1</v>
-      </c>
-      <c r="T4" s="3">
-        <v>13</v>
-      </c>
-      <c r="U4" s="3">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
@@ -890,12 +901,6 @@
         <f t="shared" si="0"/>
         <v>1.6</v>
       </c>
-      <c r="T5" s="3">
-        <v>1</v>
-      </c>
-      <c r="U5" s="3">
-        <v>3</v>
-      </c>
     </row>
     <row r="6" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -940,12 +945,6 @@
         <f t="shared" si="0"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="T6" s="3">
-        <v>2</v>
-      </c>
-      <c r="U6" s="3">
-        <v>4</v>
-      </c>
     </row>
     <row r="7" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
@@ -983,12 +982,6 @@
       <c r="S7" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
-      </c>
-      <c r="T7" s="3">
-        <v>3</v>
-      </c>
-      <c r="U7" s="3">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
@@ -1030,12 +1023,6 @@
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T8" s="3">
-        <v>4</v>
-      </c>
-      <c r="U8" s="3">
-        <v>6</v>
-      </c>
     </row>
     <row r="9" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
@@ -1076,12 +1063,6 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T9" s="3">
-        <v>5</v>
-      </c>
-      <c r="U9" s="3">
-        <v>7</v>
-      </c>
     </row>
     <row r="10" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
@@ -1120,12 +1101,6 @@
         <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
-      <c r="T10" s="3">
-        <v>6</v>
-      </c>
-      <c r="U10" s="3">
-        <v>8</v>
-      </c>
     </row>
     <row r="11" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
@@ -1150,6 +1125,9 @@
       <c r="H11" s="2">
         <v>17</v>
       </c>
+      <c r="L11" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="P11" s="3">
         <v>18</v>
       </c>
@@ -1164,12 +1142,6 @@
         <f t="shared" ref="S11:S31" si="2">Q10</f>
         <v>4</v>
       </c>
-      <c r="T11" s="3">
-        <v>7</v>
-      </c>
-      <c r="U11" s="3">
-        <v>9</v>
-      </c>
     </row>
     <row r="12" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
@@ -1214,12 +1186,6 @@
         <f t="shared" ref="S12:S16" si="4">Q11</f>
         <v>2.5</v>
       </c>
-      <c r="T12" s="3">
-        <v>8</v>
-      </c>
-      <c r="U12" s="3">
-        <v>10</v>
-      </c>
     </row>
     <row r="13" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
@@ -1244,6 +1210,9 @@
       <c r="H13" s="2">
         <v>7.5</v>
       </c>
+      <c r="L13" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="P13" s="3">
         <v>14.5</v>
       </c>
@@ -1258,12 +1227,6 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="T13" s="3">
-        <v>9</v>
-      </c>
-      <c r="U13" s="3">
-        <v>11</v>
-      </c>
     </row>
     <row r="14" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1302,12 +1265,6 @@
         <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
-      <c r="T14" s="3">
-        <v>10</v>
-      </c>
-      <c r="U14" s="3">
-        <v>12</v>
-      </c>
     </row>
     <row r="15" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -1345,12 +1302,6 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="T15" s="3">
-        <v>11</v>
-      </c>
-      <c r="U15" s="3">
-        <v>13</v>
-      </c>
     </row>
     <row r="16" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
@@ -1397,14 +1348,8 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="T16" s="3">
-        <v>12</v>
-      </c>
-      <c r="U16" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
@@ -1443,14 +1388,8 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="T17" s="3">
-        <v>13</v>
-      </c>
-      <c r="U17" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
@@ -1474,6 +1413,9 @@
       </c>
       <c r="H18" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="P18" s="3">
         <v>8</v>
@@ -1489,14 +1431,8 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="T18" s="3">
-        <v>14</v>
-      </c>
-      <c r="U18" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>20</v>
       </c>
@@ -1541,14 +1477,8 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="T19" s="3">
-        <v>15</v>
-      </c>
-      <c r="U19" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
@@ -1572,6 +1502,9 @@
       </c>
       <c r="H20" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="P20" s="3">
         <v>6</v>
@@ -1587,14 +1520,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="T20" s="3">
-        <v>16</v>
-      </c>
-      <c r="U20" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -1633,14 +1560,8 @@
         <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
-      <c r="T21" s="3">
-        <v>17</v>
-      </c>
-      <c r="U21" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
@@ -1682,14 +1603,8 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="T22" s="3">
-        <v>18</v>
-      </c>
-      <c r="U22" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
@@ -1728,14 +1643,8 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="T23" s="3">
-        <v>19</v>
-      </c>
-      <c r="U23" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
@@ -1759,6 +1668,9 @@
       </c>
       <c r="H24" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="P24" s="3">
         <f>P23</f>
@@ -1776,14 +1688,8 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="T24" s="3">
-        <v>20</v>
-      </c>
-      <c r="U24" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>20</v>
       </c>
@@ -1830,14 +1736,8 @@
         <f t="shared" si="2"/>
         <v>4.5999999999999996</v>
       </c>
-      <c r="T25" s="3">
-        <v>21</v>
-      </c>
-      <c r="U25" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>20</v>
       </c>
@@ -1861,6 +1761,9 @@
       </c>
       <c r="H26" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="P26" s="3">
         <f t="shared" si="6"/>
@@ -1878,14 +1781,8 @@
         <f t="shared" si="2"/>
         <v>5.1999999999999993</v>
       </c>
-      <c r="T26" s="3">
-        <v>22</v>
-      </c>
-      <c r="U26" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>20</v>
       </c>
@@ -1926,14 +1823,8 @@
         <f t="shared" si="2"/>
         <v>5.7999999999999989</v>
       </c>
-      <c r="T27" s="3">
-        <v>23</v>
-      </c>
-      <c r="U27" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>20</v>
       </c>
@@ -1974,14 +1865,8 @@
         <f t="shared" si="2"/>
         <v>6.3999999999999986</v>
       </c>
-      <c r="T28" s="3">
-        <v>24</v>
-      </c>
-      <c r="U28" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>20</v>
       </c>
@@ -2022,14 +1907,8 @@
         <f t="shared" si="2"/>
         <v>6.9999999999999982</v>
       </c>
-      <c r="T29" s="3">
-        <v>25</v>
-      </c>
-      <c r="U29" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>20</v>
       </c>
@@ -2070,14 +1949,8 @@
         <f t="shared" si="2"/>
         <v>7.5999999999999979</v>
       </c>
-      <c r="T30" s="3">
-        <v>26</v>
-      </c>
-      <c r="U30" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>20</v>
       </c>
@@ -2124,14 +1997,8 @@
         <f t="shared" si="2"/>
         <v>8.1999999999999975</v>
       </c>
-      <c r="T31" s="3">
-        <v>27</v>
-      </c>
-      <c r="U31" s="3">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>20</v>
       </c>
@@ -2169,14 +2036,8 @@
         <f>Q31+0.6</f>
         <v>9.3999999999999968</v>
       </c>
-      <c r="T32" s="3">
-        <v>28</v>
-      </c>
-      <c r="U32" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>20</v>
       </c>
@@ -2197,6 +2058,9 @@
       </c>
       <c r="H33" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="P33" s="3">
         <f t="shared" ref="P33:P61" si="8">R32</f>
@@ -2214,14 +2078,8 @@
         <f t="shared" ref="S33:S35" si="10">S32+0.6</f>
         <v>9.9999999999999964</v>
       </c>
-      <c r="T33" s="3">
-        <v>29</v>
-      </c>
-      <c r="U33" s="3">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>20</v>
       </c>
@@ -2265,14 +2123,8 @@
         <f t="shared" si="10"/>
         <v>10.599999999999996</v>
       </c>
-      <c r="T34" s="3">
-        <v>30</v>
-      </c>
-      <c r="U34" s="3">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>20</v>
       </c>
@@ -2293,6 +2145,9 @@
       </c>
       <c r="H35" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="P35" s="3">
         <f t="shared" si="8"/>
@@ -2310,14 +2165,8 @@
         <f t="shared" si="10"/>
         <v>11.199999999999996</v>
       </c>
-      <c r="T35" s="3">
-        <v>31</v>
-      </c>
-      <c r="U35" s="3">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>20</v>
       </c>
@@ -2355,14 +2204,8 @@
         <f>S35+0.8</f>
         <v>11.999999999999996</v>
       </c>
-      <c r="T36" s="3">
-        <v>32</v>
-      </c>
-      <c r="U36" s="3">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>20</v>
       </c>
@@ -2400,14 +2243,8 @@
         <f t="shared" ref="S37:S38" si="12">S36+0.8</f>
         <v>12.799999999999997</v>
       </c>
-      <c r="T37" s="3">
-        <v>33</v>
-      </c>
-      <c r="U37" s="3">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>20</v>
       </c>
@@ -2445,14 +2282,8 @@
         <f t="shared" si="12"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T38" s="3">
-        <v>34</v>
-      </c>
-      <c r="U38" s="3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>20</v>
       </c>
@@ -2493,14 +2324,8 @@
         <f>S38</f>
         <v>13.599999999999998</v>
       </c>
-      <c r="T39" s="3">
-        <v>35</v>
-      </c>
-      <c r="U39" s="3">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>20</v>
       </c>
@@ -2541,14 +2366,8 @@
         <f t="shared" ref="S40:S60" si="14">S39</f>
         <v>13.599999999999998</v>
       </c>
-      <c r="T40" s="3">
-        <v>36</v>
-      </c>
-      <c r="U40" s="3">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>20</v>
       </c>
@@ -2572,6 +2391,9 @@
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="P41" s="3">
         <f t="shared" si="8"/>
@@ -2589,14 +2411,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T41" s="3">
-        <v>37</v>
-      </c>
-      <c r="U41" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>20</v>
       </c>
@@ -2643,14 +2459,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T42" s="3">
-        <v>38</v>
-      </c>
-      <c r="U42" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>20</v>
       </c>
@@ -2674,6 +2484,9 @@
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="P43" s="3">
         <f t="shared" si="8"/>
@@ -2691,14 +2504,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T43" s="3">
-        <v>39</v>
-      </c>
-      <c r="U43" s="3">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>20</v>
       </c>
@@ -2739,14 +2546,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T44" s="3">
-        <v>40</v>
-      </c>
-      <c r="U44" s="3">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>20</v>
       </c>
@@ -2787,14 +2588,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T45" s="3">
-        <v>41</v>
-      </c>
-      <c r="U45" s="3">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>20</v>
       </c>
@@ -2835,14 +2630,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T46" s="3">
-        <v>42</v>
-      </c>
-      <c r="U46" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>20</v>
       </c>
@@ -2883,14 +2672,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T47" s="3">
-        <v>43</v>
-      </c>
-      <c r="U47" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>20</v>
       </c>
@@ -2931,14 +2714,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T48" s="3">
-        <v>44</v>
-      </c>
-      <c r="U48" s="3">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>20</v>
       </c>
@@ -2979,14 +2756,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T49" s="3">
-        <v>45</v>
-      </c>
-      <c r="U49" s="3">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>20</v>
       </c>
@@ -3010,6 +2781,9 @@
       </c>
       <c r="I50" s="3" t="s">
         <v>3</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="P50" s="3">
         <f t="shared" si="8"/>
@@ -3027,14 +2801,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T50" s="3">
-        <v>46</v>
-      </c>
-      <c r="U50" s="3">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>20</v>
       </c>
@@ -3081,14 +2849,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T51" s="3">
-        <v>47</v>
-      </c>
-      <c r="U51" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>20</v>
       </c>
@@ -3112,6 +2874,9 @@
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="P52" s="3">
         <f t="shared" si="8"/>
@@ -3129,14 +2894,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T52" s="3">
-        <v>48</v>
-      </c>
-      <c r="U52" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>20</v>
       </c>
@@ -3177,14 +2936,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T53" s="3">
-        <v>49</v>
-      </c>
-      <c r="U53" s="3">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>20</v>
       </c>
@@ -3225,14 +2978,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T54" s="3">
-        <v>50</v>
-      </c>
-      <c r="U54" s="3">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="55" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>20</v>
       </c>
@@ -3273,14 +3020,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T55" s="3">
-        <v>51</v>
-      </c>
-      <c r="U55" s="3">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="56" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>20</v>
       </c>
@@ -3321,14 +3062,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T56" s="3">
-        <v>52</v>
-      </c>
-      <c r="U56" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="57" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>20</v>
       </c>
@@ -3369,14 +3104,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T57" s="3">
-        <v>53</v>
-      </c>
-      <c r="U57" s="3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="58" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>20</v>
       </c>
@@ -3417,14 +3146,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T58" s="3">
-        <v>54</v>
-      </c>
-      <c r="U58" s="3">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="59" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>20</v>
       </c>
@@ -3448,6 +3171,9 @@
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="P59" s="3">
         <f t="shared" si="8"/>
@@ -3465,14 +3191,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T59" s="3">
-        <v>55</v>
-      </c>
-      <c r="U59" s="3">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>20</v>
       </c>
@@ -3519,14 +3239,8 @@
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="T60" s="3">
-        <v>56</v>
-      </c>
-      <c r="U60" s="3">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="61" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>20</v>
       </c>
@@ -3553,6 +3267,9 @@
       </c>
       <c r="K61" s="3">
         <v>57</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="P61" s="3">
         <f t="shared" si="8"/>
@@ -3570,14 +3287,8 @@
         <f>S60+0.8</f>
         <v>14.399999999999999</v>
       </c>
-      <c r="T61" s="3">
-        <v>57</v>
-      </c>
-      <c r="U61" s="3">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="62" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>20</v>
       </c>
@@ -3615,14 +3326,8 @@
         <f t="shared" ref="S62:S65" si="18">S61+0.8</f>
         <v>15.2</v>
       </c>
-      <c r="T62" s="3">
-        <v>58</v>
-      </c>
-      <c r="U62" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>20</v>
       </c>
@@ -3660,14 +3365,8 @@
         <f t="shared" si="18"/>
         <v>16</v>
       </c>
-      <c r="T63" s="3">
-        <v>59</v>
-      </c>
-      <c r="U63" s="3">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>20</v>
       </c>
@@ -3705,14 +3404,8 @@
         <f t="shared" si="18"/>
         <v>16.8</v>
       </c>
-      <c r="T64" s="3">
-        <v>60</v>
-      </c>
-      <c r="U64" s="3">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="65" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>20</v>
       </c>
@@ -3756,14 +3449,8 @@
         <f t="shared" si="18"/>
         <v>17.600000000000001</v>
       </c>
-      <c r="T65" s="3">
-        <v>61</v>
-      </c>
-      <c r="U65" s="3">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>20</v>
       </c>
@@ -3801,14 +3488,8 @@
         <f>S65+1</f>
         <v>18.600000000000001</v>
       </c>
-      <c r="T66" s="3">
-        <v>62</v>
-      </c>
-      <c r="U66" s="3">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="67" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>20</v>
       </c>
@@ -3829,6 +3510,9 @@
       </c>
       <c r="H67" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="P67" s="3">
         <f t="shared" ref="P67:P130" si="19">R66</f>
@@ -3846,14 +3530,8 @@
         <f>S66+1</f>
         <v>19.600000000000001</v>
       </c>
-      <c r="T67" s="3">
-        <v>63</v>
-      </c>
-      <c r="U67" s="3">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="68" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>20</v>
       </c>
@@ -3897,14 +3575,8 @@
         <f>S65+4.2</f>
         <v>21.8</v>
       </c>
-      <c r="T68" s="3">
-        <v>64</v>
-      </c>
-      <c r="U68" s="3">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="69" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>20</v>
       </c>
@@ -3925,6 +3597,9 @@
       </c>
       <c r="H69" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="P69" s="3">
         <f t="shared" si="19"/>
@@ -3942,14 +3617,8 @@
         <f>S68+2.2</f>
         <v>24</v>
       </c>
-      <c r="T69" s="3">
-        <v>65</v>
-      </c>
-      <c r="U69" s="3">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="70" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>20</v>
       </c>
@@ -3987,14 +3656,8 @@
         <f>S69+1</f>
         <v>25</v>
       </c>
-      <c r="T70" s="3">
-        <v>66</v>
-      </c>
-      <c r="U70" s="3">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="71" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>20</v>
       </c>
@@ -4032,14 +3695,8 @@
         <f>S68+4.2</f>
         <v>26</v>
       </c>
-      <c r="T71" s="3">
-        <v>67</v>
-      </c>
-      <c r="U71" s="3">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="72" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>20</v>
       </c>
@@ -4077,14 +3734,8 @@
         <f>S71+1</f>
         <v>27</v>
       </c>
-      <c r="T72" s="3">
-        <v>68</v>
-      </c>
-      <c r="U72" s="3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="73" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>20</v>
       </c>
@@ -4122,14 +3773,8 @@
         <f t="shared" ref="S73:S76" si="23">S72+1</f>
         <v>28</v>
       </c>
-      <c r="T73" s="3">
-        <v>69</v>
-      </c>
-      <c r="U73" s="3">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="74" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>20</v>
       </c>
@@ -4167,14 +3812,8 @@
         <f t="shared" si="23"/>
         <v>29</v>
       </c>
-      <c r="T74" s="3">
-        <v>70</v>
-      </c>
-      <c r="U74" s="3">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="75" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>20</v>
       </c>
@@ -4195,6 +3834,9 @@
       </c>
       <c r="H75" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="P75" s="3">
         <f t="shared" si="19"/>
@@ -4212,14 +3854,8 @@
         <f t="shared" si="23"/>
         <v>30</v>
       </c>
-      <c r="T75" s="3">
-        <v>71</v>
-      </c>
-      <c r="U75" s="3">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="76" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>20</v>
       </c>
@@ -4263,14 +3899,8 @@
         <f t="shared" si="23"/>
         <v>31</v>
       </c>
-      <c r="T76" s="3">
-        <v>72</v>
-      </c>
-      <c r="U76" s="3">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="77" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>20</v>
       </c>
@@ -4294,6 +3924,9 @@
       </c>
       <c r="H77" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="P77" s="3">
         <f t="shared" si="19"/>
@@ -4311,14 +3944,8 @@
         <f>S76</f>
         <v>31</v>
       </c>
-      <c r="T77" s="3">
-        <v>73</v>
-      </c>
-      <c r="U77" s="3">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="78" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>20</v>
       </c>
@@ -4359,14 +3986,8 @@
         <f t="shared" ref="S78:S79" si="25">S77</f>
         <v>31</v>
       </c>
-      <c r="T78" s="3">
-        <v>74</v>
-      </c>
-      <c r="U78" s="3">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="79" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>20</v>
       </c>
@@ -4390,6 +4011,9 @@
       </c>
       <c r="H79" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="P79" s="3">
         <f t="shared" si="19"/>
@@ -4407,14 +4031,8 @@
         <f t="shared" si="25"/>
         <v>31</v>
       </c>
-      <c r="T79" s="3">
-        <v>75</v>
-      </c>
-      <c r="U79" s="3">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="80" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>20</v>
       </c>
@@ -4467,14 +4085,8 @@
         <f>S79</f>
         <v>31</v>
       </c>
-      <c r="T80" s="3">
-        <v>76</v>
-      </c>
-      <c r="U80" s="3">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="81" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>20</v>
       </c>
@@ -4498,6 +4110,9 @@
       </c>
       <c r="H81" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="P81" s="3">
         <f t="shared" si="19"/>
@@ -4515,14 +4130,8 @@
         <f t="shared" ref="S81:S88" si="27">S80</f>
         <v>31</v>
       </c>
-      <c r="T81" s="3">
-        <v>77</v>
-      </c>
-      <c r="U81" s="3">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="82" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>20</v>
       </c>
@@ -4563,14 +4172,8 @@
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
-      <c r="T82" s="3">
-        <v>78</v>
-      </c>
-      <c r="U82" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="83" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>20</v>
       </c>
@@ -4611,14 +4214,8 @@
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
-      <c r="T83" s="3">
-        <v>79</v>
-      </c>
-      <c r="U83" s="3">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="84" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>20</v>
       </c>
@@ -4659,14 +4256,8 @@
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
-      <c r="T84" s="3">
-        <v>80</v>
-      </c>
-      <c r="U84" s="3">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="85" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>20</v>
       </c>
@@ -4707,14 +4298,8 @@
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
-      <c r="T85" s="3">
-        <v>81</v>
-      </c>
-      <c r="U85" s="3">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="86" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>20</v>
       </c>
@@ -4755,14 +4340,8 @@
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
-      <c r="T86" s="3">
-        <v>82</v>
-      </c>
-      <c r="U86" s="3">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="87" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>20</v>
       </c>
@@ -4803,14 +4382,8 @@
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
-      <c r="T87" s="3">
-        <v>83</v>
-      </c>
-      <c r="U87" s="3">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="88" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>20</v>
       </c>
@@ -4857,14 +4430,8 @@
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
-      <c r="T88" s="3">
-        <v>84</v>
-      </c>
-      <c r="U88" s="3">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="89" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>20</v>
       </c>
@@ -4905,14 +4472,8 @@
         <f>S88</f>
         <v>31</v>
       </c>
-      <c r="T89" s="3">
-        <v>85</v>
-      </c>
-      <c r="U89" s="3">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="90" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>20</v>
       </c>
@@ -4936,6 +4497,9 @@
       </c>
       <c r="H90" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L90" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="P90" s="3">
         <f>R89</f>
@@ -4953,14 +4517,8 @@
         <f t="shared" ref="S90:S91" si="29">S89</f>
         <v>31</v>
       </c>
-      <c r="T90" s="3">
-        <v>86</v>
-      </c>
-      <c r="U90" s="3">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="91" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>20</v>
       </c>
@@ -5007,14 +4565,8 @@
         <f t="shared" si="29"/>
         <v>31</v>
       </c>
-      <c r="T91" s="3">
-        <v>87</v>
-      </c>
-      <c r="U91" s="3">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="92" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>20</v>
       </c>
@@ -5035,6 +4587,9 @@
       </c>
       <c r="H92" s="2">
         <v>0.125</v>
+      </c>
+      <c r="L92" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="P92" s="3">
         <f t="shared" si="19"/>
@@ -5052,14 +4607,8 @@
         <f>S91-0.8</f>
         <v>30.2</v>
       </c>
-      <c r="T92" s="3">
-        <v>88</v>
-      </c>
-      <c r="U92" s="3">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="93" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>20</v>
       </c>
@@ -5097,14 +4646,8 @@
         <f t="shared" ref="S93:S97" si="31">S92-0.8</f>
         <v>29.4</v>
       </c>
-      <c r="T93" s="3">
-        <v>89</v>
-      </c>
-      <c r="U93" s="3">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="94" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>20</v>
       </c>
@@ -5142,14 +4685,8 @@
         <f t="shared" si="31"/>
         <v>28.599999999999998</v>
       </c>
-      <c r="T94" s="3">
-        <v>90</v>
-      </c>
-      <c r="U94" s="3">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="95" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>20</v>
       </c>
@@ -5187,14 +4724,8 @@
         <f t="shared" si="31"/>
         <v>27.799999999999997</v>
       </c>
-      <c r="T95" s="3">
-        <v>91</v>
-      </c>
-      <c r="U95" s="3">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="96" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>20</v>
       </c>
@@ -5232,14 +4763,8 @@
         <f t="shared" si="31"/>
         <v>26.999999999999996</v>
       </c>
-      <c r="T96" s="3">
-        <v>92</v>
-      </c>
-      <c r="U96" s="3">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="97" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>20</v>
       </c>
@@ -5277,14 +4802,8 @@
         <f t="shared" si="31"/>
         <v>26.199999999999996</v>
       </c>
-      <c r="T97" s="3">
-        <v>93</v>
-      </c>
-      <c r="U97" s="3">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="98" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>20</v>
       </c>
@@ -5305,6 +4824,9 @@
       </c>
       <c r="H98" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L98" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="P98" s="3">
         <f t="shared" si="19"/>
@@ -5322,14 +4844,8 @@
         <f>S97+0.8</f>
         <v>26.999999999999996</v>
       </c>
-      <c r="T98" s="3">
-        <v>94</v>
-      </c>
-      <c r="U98" s="3">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="99" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>20</v>
       </c>
@@ -5373,14 +4889,8 @@
         <f t="shared" ref="S99:S100" si="33">S98+0.8</f>
         <v>27.799999999999997</v>
       </c>
-      <c r="T99" s="3">
-        <v>95</v>
-      </c>
-      <c r="U99" s="3">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="100" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>20</v>
       </c>
@@ -5401,6 +4911,9 @@
       </c>
       <c r="H100" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="P100" s="3">
         <f t="shared" si="19"/>
@@ -5418,14 +4931,8 @@
         <f t="shared" si="33"/>
         <v>28.599999999999998</v>
       </c>
-      <c r="T100" s="3">
-        <v>96</v>
-      </c>
-      <c r="U100" s="3">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="101" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>20</v>
       </c>
@@ -5463,14 +4970,8 @@
         <f>S100+0.8</f>
         <v>29.4</v>
       </c>
-      <c r="T101" s="3">
-        <v>97</v>
-      </c>
-      <c r="U101" s="3">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="102" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>20</v>
       </c>
@@ -5508,14 +5009,8 @@
         <f t="shared" ref="S102:S103" si="35">S101+0.8</f>
         <v>30.2</v>
       </c>
-      <c r="T102" s="3">
-        <v>98</v>
-      </c>
-      <c r="U102" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="103" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>20</v>
       </c>
@@ -5553,14 +5048,8 @@
         <f t="shared" si="35"/>
         <v>31</v>
       </c>
-      <c r="T103" s="3">
-        <v>99</v>
-      </c>
-      <c r="U103" s="3">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="104" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>20</v>
       </c>
@@ -5594,14 +5083,8 @@
       <c r="S104" s="3">
         <v>29</v>
       </c>
-      <c r="T104" s="3">
-        <v>77</v>
-      </c>
-      <c r="U104" s="3">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="105" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>20</v>
       </c>
@@ -5637,14 +5120,8 @@
       <c r="S105" s="3">
         <v>29</v>
       </c>
-      <c r="T105" s="3">
-        <v>101</v>
-      </c>
-      <c r="U105" s="3">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="106" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>20</v>
       </c>
@@ -5680,14 +5157,8 @@
       <c r="S106" s="3">
         <v>29</v>
       </c>
-      <c r="T106" s="3">
-        <v>102</v>
-      </c>
-      <c r="U106" s="3">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="107" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>20</v>
       </c>
@@ -5708,6 +5179,9 @@
       </c>
       <c r="H107" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L107" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="P107" s="3">
         <f t="shared" si="19"/>
@@ -5723,14 +5197,8 @@
       <c r="S107" s="3">
         <v>29</v>
       </c>
-      <c r="T107" s="3">
-        <v>103</v>
-      </c>
-      <c r="U107" s="3">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="108" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>20</v>
       </c>
@@ -5774,14 +5242,8 @@
         <f>S107-1</f>
         <v>28</v>
       </c>
-      <c r="T108" s="3">
-        <v>104</v>
-      </c>
-      <c r="U108" s="3">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="109" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>20</v>
       </c>
@@ -5802,6 +5264,9 @@
       </c>
       <c r="H109" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L109" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="P109" s="3">
         <f t="shared" si="19"/>
@@ -5819,14 +5284,8 @@
         <f t="shared" ref="S109:S112" si="37">S108-1</f>
         <v>27</v>
       </c>
-      <c r="T109" s="3">
-        <v>105</v>
-      </c>
-      <c r="U109" s="3">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="110" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>20</v>
       </c>
@@ -5864,14 +5323,8 @@
         <f t="shared" si="37"/>
         <v>26</v>
       </c>
-      <c r="T110" s="3">
-        <v>106</v>
-      </c>
-      <c r="U110" s="3">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="111" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>20</v>
       </c>
@@ -5912,14 +5365,8 @@
         <f t="shared" si="37"/>
         <v>25</v>
       </c>
-      <c r="T111" s="3">
-        <v>107</v>
-      </c>
-      <c r="U111" s="3">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="112" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>20</v>
       </c>
@@ -5957,14 +5404,8 @@
         <f t="shared" si="37"/>
         <v>24</v>
       </c>
-      <c r="T112" s="3">
-        <v>108</v>
-      </c>
-      <c r="U112" s="3">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="113" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>20</v>
       </c>
@@ -6002,14 +5443,8 @@
         <f>S112-0.7</f>
         <v>23.3</v>
       </c>
-      <c r="T113" s="3">
-        <v>109</v>
-      </c>
-      <c r="U113" s="3">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="114" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>20</v>
       </c>
@@ -6047,14 +5482,8 @@
         <f t="shared" ref="S114:S119" si="39">S113-0.7</f>
         <v>22.6</v>
       </c>
-      <c r="T114" s="3">
-        <v>110</v>
-      </c>
-      <c r="U114" s="3">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="115" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>20</v>
       </c>
@@ -6092,14 +5521,8 @@
         <f t="shared" si="39"/>
         <v>21.900000000000002</v>
       </c>
-      <c r="T115" s="3">
-        <v>111</v>
-      </c>
-      <c r="U115" s="3">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="116" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>20</v>
       </c>
@@ -6120,6 +5543,9 @@
       </c>
       <c r="H116" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L116" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="P116" s="3">
         <f t="shared" si="19"/>
@@ -6137,14 +5563,8 @@
         <f t="shared" si="39"/>
         <v>21.200000000000003</v>
       </c>
-      <c r="T116" s="3">
-        <v>112</v>
-      </c>
-      <c r="U116" s="3">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="117" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>20</v>
       </c>
@@ -6188,14 +5608,8 @@
         <f t="shared" si="39"/>
         <v>20.500000000000004</v>
       </c>
-      <c r="T117" s="3">
-        <v>113</v>
-      </c>
-      <c r="U117" s="3">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="118" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>20</v>
       </c>
@@ -6216,6 +5630,9 @@
       </c>
       <c r="H118" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L118" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="P118" s="3">
         <f t="shared" si="19"/>
@@ -6233,14 +5650,8 @@
         <f t="shared" si="39"/>
         <v>19.800000000000004</v>
       </c>
-      <c r="T118" s="3">
-        <v>114</v>
-      </c>
-      <c r="U118" s="3">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="119" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>20</v>
       </c>
@@ -6278,14 +5689,8 @@
         <f t="shared" si="39"/>
         <v>19.100000000000005</v>
       </c>
-      <c r="T119" s="3">
-        <v>115</v>
-      </c>
-      <c r="U119" s="3">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="120" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>20</v>
       </c>
@@ -6323,14 +5728,8 @@
         <f>S119-0.8</f>
         <v>18.300000000000004</v>
       </c>
-      <c r="T120" s="3">
-        <v>116</v>
-      </c>
-      <c r="U120" s="3">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="121" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>20</v>
       </c>
@@ -6368,14 +5767,8 @@
         <f t="shared" ref="S121:S124" si="40">S120-0.8</f>
         <v>17.500000000000004</v>
       </c>
-      <c r="T121" s="3">
-        <v>117</v>
-      </c>
-      <c r="U121" s="3">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="122" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>20</v>
       </c>
@@ -6413,14 +5806,8 @@
         <f t="shared" si="40"/>
         <v>16.700000000000003</v>
       </c>
-      <c r="T122" s="3">
-        <v>118</v>
-      </c>
-      <c r="U122" s="3">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="123" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>20</v>
       </c>
@@ -6458,14 +5845,8 @@
         <f t="shared" si="40"/>
         <v>15.900000000000002</v>
       </c>
-      <c r="T123" s="3">
-        <v>119</v>
-      </c>
-      <c r="U123" s="3">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="124" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>20</v>
       </c>
@@ -6503,14 +5884,8 @@
         <f t="shared" si="40"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T124" s="3">
-        <v>120</v>
-      </c>
-      <c r="U124" s="3">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="125" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>20</v>
       </c>
@@ -6534,6 +5909,9 @@
       </c>
       <c r="I125" s="3" t="s">
         <v>3</v>
+      </c>
+      <c r="L125" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="P125" s="3">
         <f t="shared" si="19"/>
@@ -6551,14 +5929,8 @@
         <f>S124</f>
         <v>15.100000000000001</v>
       </c>
-      <c r="T125" s="3">
-        <v>121</v>
-      </c>
-      <c r="U125" s="3">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="126" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>20</v>
       </c>
@@ -6605,14 +5977,8 @@
         <f t="shared" ref="S126:S146" si="43">S125</f>
         <v>15.100000000000001</v>
       </c>
-      <c r="T126" s="3">
-        <v>122</v>
-      </c>
-      <c r="U126" s="3">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="127" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>20</v>
       </c>
@@ -6636,6 +6002,9 @@
       </c>
       <c r="I127" s="3" t="s">
         <v>3</v>
+      </c>
+      <c r="L127" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="P127" s="3">
         <f t="shared" si="19"/>
@@ -6653,14 +6022,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T127" s="3">
-        <v>123</v>
-      </c>
-      <c r="U127" s="3">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="128" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>20</v>
       </c>
@@ -6701,14 +6064,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T128" s="3">
-        <v>124</v>
-      </c>
-      <c r="U128" s="3">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="129" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>20</v>
       </c>
@@ -6749,14 +6106,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T129" s="3">
-        <v>125</v>
-      </c>
-      <c r="U129" s="3">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="130" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>20</v>
       </c>
@@ -6797,14 +6148,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T130" s="3">
-        <v>126</v>
-      </c>
-      <c r="U130" s="3">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="131" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>20</v>
       </c>
@@ -6845,14 +6190,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T131" s="3">
-        <v>127</v>
-      </c>
-      <c r="U131" s="3">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="132" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>20</v>
       </c>
@@ -6893,14 +6232,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T132" s="3">
-        <v>128</v>
-      </c>
-      <c r="U132" s="3">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="133" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="133" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>20</v>
       </c>
@@ -6941,14 +6274,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T133" s="3">
-        <v>129</v>
-      </c>
-      <c r="U133" s="3">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="134" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>20</v>
       </c>
@@ -6972,6 +6299,9 @@
       </c>
       <c r="I134" s="3" t="s">
         <v>3</v>
+      </c>
+      <c r="L134" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="P134" s="3">
         <f t="shared" si="44"/>
@@ -6989,14 +6319,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T134" s="3">
-        <v>130</v>
-      </c>
-      <c r="U134" s="3">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="135" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>20</v>
       </c>
@@ -7043,14 +6367,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T135" s="3">
-        <v>131</v>
-      </c>
-      <c r="U135" s="3">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="136" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="136" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>20</v>
       </c>
@@ -7074,6 +6392,9 @@
       </c>
       <c r="I136" s="3" t="s">
         <v>3</v>
+      </c>
+      <c r="L136" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="P136" s="3">
         <f t="shared" si="44"/>
@@ -7091,14 +6412,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T136" s="3">
-        <v>132</v>
-      </c>
-      <c r="U136" s="3">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="137" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="137" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>20</v>
       </c>
@@ -7139,14 +6454,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T137" s="3">
-        <v>133</v>
-      </c>
-      <c r="U137" s="3">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="138" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="138" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>20</v>
       </c>
@@ -7187,14 +6496,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T138" s="3">
-        <v>134</v>
-      </c>
-      <c r="U138" s="3">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="139" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>20</v>
       </c>
@@ -7235,14 +6538,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T139" s="3">
-        <v>135</v>
-      </c>
-      <c r="U139" s="3">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="140" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>20</v>
       </c>
@@ -7283,14 +6580,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T140" s="3">
-        <v>136</v>
-      </c>
-      <c r="U140" s="3">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="141" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="141" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>20</v>
       </c>
@@ -7331,14 +6622,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T141" s="3">
-        <v>137</v>
-      </c>
-      <c r="U141" s="3">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="142" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>20</v>
       </c>
@@ -7379,14 +6664,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T142" s="3">
-        <v>138</v>
-      </c>
-      <c r="U142" s="3">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="143" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="143" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>20</v>
       </c>
@@ -7410,6 +6689,9 @@
       </c>
       <c r="I143" s="3" t="s">
         <v>3</v>
+      </c>
+      <c r="L143" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="P143" s="3">
         <f t="shared" si="44"/>
@@ -7427,14 +6709,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T143" s="3">
-        <v>139</v>
-      </c>
-      <c r="U143" s="3">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="144" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="144" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>20</v>
       </c>
@@ -7481,14 +6757,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T144" s="3">
-        <v>140</v>
-      </c>
-      <c r="U144" s="3">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="145" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>20</v>
       </c>
@@ -7512,6 +6782,9 @@
       </c>
       <c r="I145" s="3" t="s">
         <v>3</v>
+      </c>
+      <c r="L145" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="P145" s="3">
         <f t="shared" si="44"/>
@@ -7529,14 +6802,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T145" s="3">
-        <v>141</v>
-      </c>
-      <c r="U145" s="3">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="146" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>20</v>
       </c>
@@ -7577,14 +6844,8 @@
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="T146" s="3">
-        <v>142</v>
-      </c>
-      <c r="U146" s="3">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="147" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="147" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>20</v>
       </c>
@@ -7622,14 +6883,8 @@
         <f>S146-0.7</f>
         <v>14.400000000000002</v>
       </c>
-      <c r="T147" s="3">
-        <v>143</v>
-      </c>
-      <c r="U147" s="3">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="148" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>20</v>
       </c>
@@ -7667,14 +6922,8 @@
         <f t="shared" ref="S148:S149" si="47">S147-0.7</f>
         <v>13.700000000000003</v>
       </c>
-      <c r="T148" s="3">
-        <v>144</v>
-      </c>
-      <c r="U148" s="3">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="149" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="149" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>20</v>
       </c>
@@ -7712,14 +6961,8 @@
         <f t="shared" si="47"/>
         <v>13.000000000000004</v>
       </c>
-      <c r="T149" s="3">
-        <v>145</v>
-      </c>
-      <c r="U149" s="3">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="150" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>20</v>
       </c>
@@ -7757,14 +7000,8 @@
         <f>S149-0.8</f>
         <v>12.200000000000003</v>
       </c>
-      <c r="T150" s="3">
-        <v>146</v>
-      </c>
-      <c r="U150" s="3">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="151" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="151" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>20</v>
       </c>
@@ -7802,14 +7039,8 @@
         <f t="shared" ref="S151:S152" si="49">S150-0.8</f>
         <v>11.400000000000002</v>
       </c>
-      <c r="T151" s="3">
-        <v>147</v>
-      </c>
-      <c r="U151" s="3">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="152" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>20</v>
       </c>
@@ -7847,14 +7078,8 @@
         <f t="shared" si="49"/>
         <v>10.600000000000001</v>
       </c>
-      <c r="T152" s="3">
-        <v>148</v>
-      </c>
-      <c r="U152" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="153" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>20</v>
       </c>
@@ -7890,17 +7115,11 @@
       <c r="S153" s="3">
         <v>8.8000000000000007</v>
       </c>
-      <c r="T153" s="3">
-        <v>149</v>
-      </c>
-      <c r="U153" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="H155"/>
     </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="H156"/>
     </row>
   </sheetData>

--- a/TrackModel/Green Line.xlsx
+++ b/TrackModel/Green Line.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pitt-my.sharepoint.com/personal/dgs44_pitt_edu/Documents/Trains/TrackModel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="608" documentId="8_{D0660D75-C052-4898-8402-12AA78E71664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50BA1C67-8B17-4746-87A0-AC8F3AF98ADC}"/>
+  <xr:revisionPtr revIDLastSave="680" documentId="8_{D0660D75-C052-4898-8402-12AA78E71664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6B8BD8C-0824-4FB3-96FB-EC0CF953EC59}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C71A2FFE-490E-4D57-BAA4-DE7AC575C897}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{C71A2FFE-490E-4D57-BAA4-DE7AC575C897}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="76">
   <si>
     <t>A</t>
   </si>
@@ -218,43 +218,52 @@
     <t>Yard</t>
   </si>
   <si>
-    <t>Edgebrook,L</t>
-  </si>
-  <si>
-    <t>Whited,LR</t>
-  </si>
-  <si>
-    <t>Station,LR</t>
-  </si>
-  <si>
-    <t>South Bank,L</t>
-  </si>
-  <si>
-    <t>Central,R</t>
-  </si>
-  <si>
-    <t>Inglewood,R</t>
-  </si>
-  <si>
-    <t>Overbrook,R</t>
-  </si>
-  <si>
-    <t>Glenbury,R</t>
-  </si>
-  <si>
-    <t>Dormont,R</t>
-  </si>
-  <si>
-    <t>Mt Lebanon,LR</t>
-  </si>
-  <si>
-    <t>Poplar,L</t>
-  </si>
-  <si>
-    <t>Castle Shannon,L</t>
-  </si>
-  <si>
-    <t>Inglewood,L</t>
+    <t>LXPioneer</t>
+  </si>
+  <si>
+    <t>LXEdgebrook</t>
+  </si>
+  <si>
+    <t>LRStation</t>
+  </si>
+  <si>
+    <t>LRWhited</t>
+  </si>
+  <si>
+    <t>LXSouth Bank</t>
+  </si>
+  <si>
+    <t>XRCentral</t>
+  </si>
+  <si>
+    <t>XRInglewood</t>
+  </si>
+  <si>
+    <t>XROverbook</t>
+  </si>
+  <si>
+    <t>XRDormont</t>
+  </si>
+  <si>
+    <t>LRMt Lebanon</t>
+  </si>
+  <si>
+    <t>LXPoplar</t>
+  </si>
+  <si>
+    <t>LXCastle Shannon</t>
+  </si>
+  <si>
+    <t>XRGlenbury</t>
+  </si>
+  <si>
+    <t>XROverbrook</t>
+  </si>
+  <si>
+    <t>LXInglewood</t>
+  </si>
+  <si>
+    <t>2425262728292A2B2C2D2E2F303132333435363738397A7B7C7D7E7F808182838485868788898A8B8C8D8E8F</t>
   </si>
 </sst>
 </file>
@@ -334,6 +343,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -807,7 +820,9 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+      <c r="L3" t="s">
+        <v>75</v>
+      </c>
       <c r="M3" s="3" t="s">
         <v>59</v>
       </c>
@@ -887,6 +902,9 @@
       <c r="H5" s="2">
         <v>1.5</v>
       </c>
+      <c r="L5" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="P5" s="3">
         <v>12.3</v>
       </c>
@@ -968,6 +986,9 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2">
         <v>5</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="P7" s="3">
         <v>14</v>
@@ -1126,7 +1147,7 @@
         <v>17</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P11" s="3">
         <v>18</v>
@@ -1211,7 +1232,7 @@
         <v>7.5</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P13" s="3">
         <v>14.5</v>
@@ -1670,7 +1691,7 @@
         <v>0.5</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P24" s="3">
         <f>P23</f>
@@ -1763,7 +1784,7 @@
         <v>0.5</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P26" s="3">
         <f t="shared" si="6"/>
@@ -2060,7 +2081,7 @@
         <v>0.5</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P33" s="3">
         <f t="shared" ref="P33:P61" si="8">R32</f>
@@ -2147,7 +2168,7 @@
         <v>0.5</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P35" s="3">
         <f t="shared" si="8"/>
@@ -2393,7 +2414,7 @@
         <v>3</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P41" s="3">
         <f t="shared" si="8"/>
@@ -2486,7 +2507,7 @@
         <v>3</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P43" s="3">
         <f t="shared" si="8"/>
@@ -2783,7 +2804,7 @@
         <v>3</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P50" s="3">
         <f t="shared" si="8"/>
@@ -2876,7 +2897,7 @@
         <v>3</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P52" s="3">
         <f t="shared" si="8"/>
@@ -3173,7 +3194,7 @@
         <v>3</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P59" s="3">
         <f t="shared" si="8"/>
@@ -3269,7 +3290,7 @@
         <v>57</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P61" s="3">
         <f t="shared" si="8"/>
@@ -3511,9 +3532,6 @@
       <c r="H67" s="2">
         <v>0.5</v>
       </c>
-      <c r="L67" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="P67" s="3">
         <f t="shared" ref="P67:P130" si="19">R66</f>
         <v>22.6</v>
@@ -3598,9 +3616,6 @@
       <c r="H69" s="2">
         <v>0.5</v>
       </c>
-      <c r="L69" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="P69" s="3">
         <f t="shared" si="19"/>
         <v>22.6</v>
@@ -5545,7 +5560,7 @@
         <v>0.5</v>
       </c>
       <c r="L116" s="3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="P116" s="3">
         <f t="shared" si="19"/>
@@ -5632,7 +5647,7 @@
         <v>0.5</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="P118" s="3">
         <f t="shared" si="19"/>
@@ -5911,7 +5926,7 @@
         <v>3</v>
       </c>
       <c r="L125" s="3" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="P125" s="3">
         <f t="shared" si="19"/>
@@ -6004,7 +6019,7 @@
         <v>3</v>
       </c>
       <c r="L127" s="3" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="P127" s="3">
         <f t="shared" si="19"/>
@@ -6301,7 +6316,7 @@
         <v>3</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P134" s="3">
         <f t="shared" si="44"/>
@@ -6394,7 +6409,7 @@
         <v>3</v>
       </c>
       <c r="L136" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P136" s="3">
         <f t="shared" si="44"/>
@@ -6691,7 +6706,7 @@
         <v>3</v>
       </c>
       <c r="L143" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P143" s="3">
         <f t="shared" si="44"/>
@@ -6784,7 +6799,7 @@
         <v>3</v>
       </c>
       <c r="L145" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P145" s="3">
         <f t="shared" si="44"/>

--- a/TrackModel/Green Line.xlsx
+++ b/TrackModel/Green Line.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pitt-my.sharepoint.com/personal/dgs44_pitt_edu/Documents/Trains/TrackModel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="680" documentId="8_{D0660D75-C052-4898-8402-12AA78E71664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6B8BD8C-0824-4FB3-96FB-EC0CF953EC59}"/>
+  <xr:revisionPtr revIDLastSave="682" documentId="8_{D0660D75-C052-4898-8402-12AA78E71664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE4F6CF7-A6F0-49F6-9AFB-C0390E7FA6A8}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{C71A2FFE-490E-4D57-BAA4-DE7AC575C897}"/>
+    <workbookView minimized="1" xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11295" xr2:uid="{C71A2FFE-490E-4D57-BAA4-DE7AC575C897}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="76">
   <si>
     <t>A</t>
   </si>
@@ -343,10 +343,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3532,6 +3528,9 @@
       <c r="H67" s="2">
         <v>0.5</v>
       </c>
+      <c r="L67" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="P67" s="3">
         <f t="shared" ref="P67:P130" si="19">R66</f>
         <v>22.6</v>
@@ -3615,6 +3614,9 @@
       </c>
       <c r="H69" s="2">
         <v>0.5</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="P69" s="3">
         <f t="shared" si="19"/>

--- a/TrackModel/Green Line.xlsx
+++ b/TrackModel/Green Line.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pitt-my.sharepoint.com/personal/dgs44_pitt_edu/Documents/Trains/TrackModel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="682" documentId="8_{D0660D75-C052-4898-8402-12AA78E71664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE4F6CF7-A6F0-49F6-9AFB-C0390E7FA6A8}"/>
+  <xr:revisionPtr revIDLastSave="692" documentId="8_{D0660D75-C052-4898-8402-12AA78E71664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{214EED10-7E9C-414B-B0E9-593AE83C0A2A}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11295" xr2:uid="{C71A2FFE-490E-4D57-BAA4-DE7AC575C897}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{C71A2FFE-490E-4D57-BAA4-DE7AC575C897}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="77">
   <si>
     <t>A</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>2425262728292A2B2C2D2E2F303132333435363738397A7B7C7D7E7F808182838485868788898A8B8C8D8E8F</t>
+  </si>
+  <si>
+    <t>Signal</t>
   </si>
 </sst>
 </file>
@@ -730,6 +733,9 @@
       <c r="S1" s="3">
         <v>18</v>
       </c>
+      <c r="T1" s="3">
+        <v>19</v>
+      </c>
     </row>
     <row r="2" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -778,15 +784,18 @@
         <v>10</v>
       </c>
       <c r="P2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>58</v>
       </c>
     </row>
@@ -824,19 +833,18 @@
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
-      <c r="P3" s="3">
+      <c r="Q3" s="3">
         <v>22</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="R3" s="3">
         <v>11</v>
       </c>
-      <c r="R3" s="3">
+      <c r="S3" s="3">
         <v>22</v>
       </c>
-      <c r="S3" s="3">
+      <c r="T3" s="3">
         <v>11</v>
       </c>
-      <c r="T3" s="3"/>
       <c r="U3" s="3"/>
     </row>
     <row r="4" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
@@ -862,16 +870,16 @@
       <c r="H4" s="2">
         <v>0.5</v>
       </c>
-      <c r="P4" s="3">
+      <c r="Q4" s="3">
         <v>11.7</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="R4" s="3">
         <v>1.6</v>
       </c>
-      <c r="R4" s="3">
+      <c r="S4" s="3">
         <v>11</v>
       </c>
-      <c r="S4" s="3">
+      <c r="T4" s="3">
         <v>1</v>
       </c>
     </row>
@@ -901,17 +909,17 @@
       <c r="L5" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="P5" s="3">
+      <c r="Q5" s="3">
         <v>12.3</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="R5" s="3">
         <v>2.2999999999999998</v>
       </c>
-      <c r="R5" s="3">
-        <f t="shared" ref="R5:S10" si="0">P4</f>
+      <c r="S5" s="3">
+        <f t="shared" ref="S5:T10" si="0">Q4</f>
         <v>11.7</v>
       </c>
-      <c r="S5" s="3">
+      <c r="T5" s="3">
         <f t="shared" si="0"/>
         <v>1.6</v>
       </c>
@@ -945,17 +953,17 @@
       <c r="N6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="P6" s="3">
+      <c r="Q6" s="3">
         <v>13</v>
       </c>
-      <c r="Q6" s="3">
-        <v>3</v>
-      </c>
       <c r="R6" s="3">
+        <v>3</v>
+      </c>
+      <c r="S6" s="3">
         <f t="shared" si="0"/>
         <v>12.3</v>
       </c>
-      <c r="S6" s="3">
+      <c r="T6" s="3">
         <f t="shared" si="0"/>
         <v>2.2999999999999998</v>
       </c>
@@ -986,17 +994,17 @@
       <c r="L7" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="P7" s="3">
+      <c r="Q7" s="3">
         <v>14</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="R7" s="3">
         <v>3.5</v>
       </c>
-      <c r="R7" s="3">
+      <c r="S7" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="S7" s="3">
+      <c r="T7" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1026,17 +1034,17 @@
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
@@ -1066,17 +1074,17 @@
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4.5</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1104,17 +1112,17 @@
       <c r="H10" s="2">
         <v>17</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>18</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
@@ -1145,18 +1153,18 @@
       <c r="L11" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="P11" s="3">
+      <c r="Q11" s="3">
         <v>18</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="R11" s="3">
         <v>2.5</v>
       </c>
-      <c r="R11" s="3">
-        <f t="shared" ref="R11:R31" si="1">P10</f>
+      <c r="S11" s="3">
+        <f t="shared" ref="S11:S31" si="1">Q10</f>
         <v>18</v>
       </c>
-      <c r="S11" s="3">
-        <f t="shared" ref="S11:S31" si="2">Q10</f>
+      <c r="T11" s="3">
+        <f t="shared" ref="T11:T31" si="2">R10</f>
         <v>4</v>
       </c>
     </row>
@@ -1189,18 +1197,18 @@
       <c r="N12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>16.5</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2</v>
       </c>
-      <c r="R12" s="3">
-        <f t="shared" ref="R12:R16" si="3">P11</f>
+      <c r="S12" s="3">
+        <f t="shared" ref="S12:S16" si="3">Q11</f>
         <v>18</v>
       </c>
-      <c r="S12" s="3">
-        <f t="shared" ref="S12:S16" si="4">Q11</f>
+      <c r="T12" s="3">
+        <f t="shared" ref="T12:T16" si="4">R11</f>
         <v>2.5</v>
       </c>
     </row>
@@ -1230,17 +1238,17 @@
       <c r="L13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="P13" s="3">
+      <c r="Q13" s="3">
         <v>14.5</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="R13" s="3">
         <v>1.5</v>
       </c>
-      <c r="R13" s="3">
+      <c r="S13" s="3">
         <f t="shared" si="3"/>
         <v>16.5</v>
       </c>
-      <c r="S13" s="3">
+      <c r="T13" s="3">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
@@ -1268,17 +1276,17 @@
       <c r="H14" s="2">
         <v>3.5</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>13</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <f t="shared" si="3"/>
         <v>14.5</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
@@ -1305,17 +1313,17 @@
       <c r="H15" s="2">
         <v>0.5</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>11</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -1351,22 +1359,25 @@
       <c r="K16" s="3">
         <v>12</v>
       </c>
-      <c r="P16" s="3">
+      <c r="P16" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="3">
         <v>10</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="R16" s="3">
         <v>1</v>
       </c>
-      <c r="R16" s="3">
+      <c r="S16" s="3">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="S16" s="3">
+      <c r="T16" s="3">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
@@ -1391,22 +1402,22 @@
       <c r="H17" s="2">
         <v>0.5</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1</v>
       </c>
-      <c r="R17" s="3">
-        <f t="shared" ref="R17:S19" si="5">P16</f>
+      <c r="S17" s="3">
+        <f t="shared" ref="S17:T19" si="5">Q16</f>
         <v>10</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
@@ -1434,22 +1445,22 @@
       <c r="L18" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>20</v>
       </c>
@@ -1480,22 +1491,22 @@
       <c r="N19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P19" s="3">
+      <c r="Q19" s="3">
         <v>7</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="R19" s="3">
         <v>1</v>
       </c>
-      <c r="R19" s="3">
+      <c r="S19" s="3">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="S19" s="3">
+      <c r="T19" s="3">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
@@ -1523,22 +1534,22 @@
       <c r="L20" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1.5</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -1563,22 +1574,22 @@
       <c r="H21" s="2">
         <v>0.5</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
@@ -1606,22 +1617,22 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>4.5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>3</v>
-      </c>
       <c r="R22" s="3">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
@@ -1646,22 +1657,22 @@
       <c r="H23" s="2">
         <v>0.5</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4.5</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
@@ -1689,24 +1700,24 @@
       <c r="L24" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="P24" s="3">
-        <f>P23</f>
+      <c r="Q24" s="3">
+        <f>Q23</f>
         <v>4.5</v>
       </c>
-      <c r="Q24" s="3">
-        <f>Q23+0.6</f>
+      <c r="R24" s="3">
+        <f>R23+0.6</f>
         <v>4.5999999999999996</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>20</v>
       </c>
@@ -1737,24 +1748,24 @@
       <c r="N25" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P25" s="3">
-        <f t="shared" ref="P25:P31" si="6">P24</f>
+      <c r="Q25" s="3">
+        <f t="shared" ref="Q25:Q31" si="6">Q24</f>
         <v>4.5</v>
       </c>
-      <c r="Q25" s="3">
-        <f t="shared" ref="Q25:Q31" si="7">Q24+0.6</f>
+      <c r="R25" s="3">
+        <f t="shared" ref="R25:R31" si="7">R24+0.6</f>
         <v>5.1999999999999993</v>
       </c>
-      <c r="R25" s="3">
+      <c r="S25" s="3">
         <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
-      <c r="S25" s="3">
+      <c r="T25" s="3">
         <f t="shared" si="2"/>
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>20</v>
       </c>
@@ -1782,24 +1793,24 @@
       <c r="L26" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <f t="shared" si="6"/>
         <v>4.5</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <f t="shared" si="7"/>
         <v>5.7999999999999989</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <f t="shared" si="2"/>
         <v>5.1999999999999993</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>20</v>
       </c>
@@ -1824,24 +1835,24 @@
       <c r="H27" s="2">
         <v>0.5</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <f t="shared" si="6"/>
         <v>4.5</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <f t="shared" si="7"/>
         <v>6.3999999999999986</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <f t="shared" si="2"/>
         <v>5.7999999999999989</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>20</v>
       </c>
@@ -1866,24 +1877,24 @@
       <c r="H28" s="2">
         <v>0.5</v>
       </c>
-      <c r="P28" s="3">
+      <c r="Q28" s="3">
         <f t="shared" si="6"/>
         <v>4.5</v>
       </c>
-      <c r="Q28" s="3">
+      <c r="R28" s="3">
         <f t="shared" si="7"/>
         <v>6.9999999999999982</v>
       </c>
-      <c r="R28" s="3">
+      <c r="S28" s="3">
         <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
-      <c r="S28" s="3">
+      <c r="T28" s="3">
         <f t="shared" si="2"/>
         <v>6.3999999999999986</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>20</v>
       </c>
@@ -1908,24 +1919,24 @@
       <c r="H29" s="2">
         <v>0.5</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <f t="shared" si="6"/>
         <v>4.5</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <f t="shared" si="7"/>
         <v>7.5999999999999979</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <f t="shared" si="2"/>
         <v>6.9999999999999982</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>20</v>
       </c>
@@ -1950,24 +1961,24 @@
       <c r="H30" s="2">
         <v>0.5</v>
       </c>
-      <c r="P30" s="3">
+      <c r="Q30" s="3">
         <f t="shared" si="6"/>
         <v>4.5</v>
       </c>
-      <c r="Q30" s="3">
+      <c r="R30" s="3">
         <f t="shared" si="7"/>
         <v>8.1999999999999975</v>
       </c>
-      <c r="R30" s="3">
+      <c r="S30" s="3">
         <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
-      <c r="S30" s="3">
+      <c r="T30" s="3">
         <f t="shared" si="2"/>
         <v>7.5999999999999979</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>20</v>
       </c>
@@ -1998,24 +2009,27 @@
       <c r="K31" s="3">
         <v>150</v>
       </c>
-      <c r="P31" s="3">
+      <c r="P31" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q31" s="3">
         <f t="shared" si="6"/>
         <v>4.5</v>
       </c>
-      <c r="Q31" s="3">
+      <c r="R31" s="3">
         <f t="shared" si="7"/>
         <v>8.7999999999999972</v>
       </c>
-      <c r="R31" s="3">
+      <c r="S31" s="3">
         <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
-      <c r="S31" s="3">
+      <c r="T31" s="3">
         <f t="shared" si="2"/>
         <v>8.1999999999999975</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>20</v>
       </c>
@@ -2037,24 +2051,24 @@
       <c r="H32" s="2">
         <v>0.5</v>
       </c>
-      <c r="P32" s="3">
-        <f>P31</f>
-        <v>4.5</v>
-      </c>
       <c r="Q32" s="3">
         <f>Q31</f>
+        <v>4.5</v>
+      </c>
+      <c r="R32" s="3">
+        <f>R31</f>
         <v>8.7999999999999972</v>
       </c>
-      <c r="R32" s="3">
-        <f>P31</f>
+      <c r="S32" s="3">
+        <f>Q31</f>
         <v>4.5</v>
       </c>
-      <c r="S32" s="3">
-        <f>Q31+0.6</f>
+      <c r="T32" s="3">
+        <f>R31+0.6</f>
         <v>9.3999999999999968</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>20</v>
       </c>
@@ -2079,24 +2093,24 @@
       <c r="L33" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="P33" s="3">
-        <f t="shared" ref="P33:P61" si="8">R32</f>
+      <c r="Q33" s="3">
+        <f t="shared" ref="Q33:Q61" si="8">S32</f>
         <v>4.5</v>
       </c>
-      <c r="Q33" s="3">
-        <f t="shared" ref="Q33:Q61" si="9">S32</f>
+      <c r="R33" s="3">
+        <f t="shared" ref="R33:R61" si="9">T32</f>
         <v>9.3999999999999968</v>
       </c>
-      <c r="R33" s="3">
-        <f>R32</f>
+      <c r="S33" s="3">
+        <f>S32</f>
         <v>4.5</v>
       </c>
-      <c r="S33" s="3">
-        <f t="shared" ref="S33:S35" si="10">S32+0.6</f>
+      <c r="T33" s="3">
+        <f t="shared" ref="T33:T35" si="10">T32+0.6</f>
         <v>9.9999999999999964</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>20</v>
       </c>
@@ -2124,24 +2138,24 @@
       <c r="N34" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="P34" s="3">
+      <c r="Q34" s="3">
         <f t="shared" si="8"/>
         <v>4.5</v>
       </c>
-      <c r="Q34" s="3">
+      <c r="R34" s="3">
         <f t="shared" si="9"/>
         <v>9.9999999999999964</v>
       </c>
-      <c r="R34" s="3">
-        <f>R33</f>
+      <c r="S34" s="3">
+        <f>S33</f>
         <v>4.5</v>
       </c>
-      <c r="S34" s="3">
+      <c r="T34" s="3">
         <f t="shared" si="10"/>
         <v>10.599999999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>20</v>
       </c>
@@ -2166,24 +2180,24 @@
       <c r="L35" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <f t="shared" si="8"/>
         <v>4.5</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <f t="shared" si="9"/>
         <v>10.599999999999996</v>
       </c>
-      <c r="R35" s="3">
-        <f>R34</f>
+      <c r="S35" s="3">
+        <f>S34</f>
         <v>4.5</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <f t="shared" si="10"/>
         <v>11.199999999999996</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>20</v>
       </c>
@@ -2205,24 +2219,24 @@
       <c r="H36" s="2">
         <v>0.5</v>
       </c>
-      <c r="P36" s="3">
+      <c r="Q36" s="3">
         <f t="shared" si="8"/>
         <v>4.5</v>
       </c>
-      <c r="Q36" s="3">
+      <c r="R36" s="3">
         <f t="shared" si="9"/>
         <v>11.199999999999996</v>
       </c>
-      <c r="R36" s="3">
-        <f>R35+0.7</f>
+      <c r="S36" s="3">
+        <f>S35+0.7</f>
         <v>5.2</v>
       </c>
-      <c r="S36" s="3">
-        <f>S35+0.8</f>
+      <c r="T36" s="3">
+        <f>T35+0.8</f>
         <v>11.999999999999996</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>20</v>
       </c>
@@ -2244,24 +2258,24 @@
       <c r="H37" s="2">
         <v>0.5</v>
       </c>
-      <c r="P37" s="3">
+      <c r="Q37" s="3">
         <f t="shared" si="8"/>
         <v>5.2</v>
       </c>
-      <c r="Q37" s="3">
+      <c r="R37" s="3">
         <f t="shared" si="9"/>
         <v>11.999999999999996</v>
       </c>
-      <c r="R37" s="3">
-        <f t="shared" ref="R37:R38" si="11">R36+0.7</f>
+      <c r="S37" s="3">
+        <f t="shared" ref="S37:S38" si="11">S36+0.7</f>
         <v>5.9</v>
       </c>
-      <c r="S37" s="3">
-        <f t="shared" ref="S37:S38" si="12">S36+0.8</f>
+      <c r="T37" s="3">
+        <f t="shared" ref="T37:T38" si="12">T36+0.8</f>
         <v>12.799999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>20</v>
       </c>
@@ -2283,24 +2297,24 @@
       <c r="H38" s="2">
         <v>0.5</v>
       </c>
-      <c r="P38" s="3">
+      <c r="Q38" s="3">
         <f t="shared" si="8"/>
         <v>5.9</v>
       </c>
-      <c r="Q38" s="3">
+      <c r="R38" s="3">
         <f t="shared" si="9"/>
         <v>12.799999999999997</v>
       </c>
-      <c r="R38" s="3">
+      <c r="S38" s="3">
         <f t="shared" si="11"/>
         <v>6.6000000000000005</v>
       </c>
-      <c r="S38" s="3">
+      <c r="T38" s="3">
         <f t="shared" si="12"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>20</v>
       </c>
@@ -2325,24 +2339,24 @@
       <c r="I39" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P39" s="3">
+      <c r="Q39" s="3">
         <f t="shared" si="8"/>
         <v>6.6000000000000005</v>
       </c>
-      <c r="Q39" s="3">
+      <c r="R39" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R39" s="3">
-        <f>R38+0.5</f>
+      <c r="S39" s="3">
+        <f>S38+0.5</f>
         <v>7.1000000000000005</v>
       </c>
-      <c r="S39" s="3">
-        <f>S38</f>
+      <c r="T39" s="3">
+        <f>T38</f>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>20</v>
       </c>
@@ -2367,24 +2381,24 @@
       <c r="I40" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P40" s="3">
+      <c r="Q40" s="3">
         <f t="shared" si="8"/>
         <v>7.1000000000000005</v>
       </c>
-      <c r="Q40" s="3">
+      <c r="R40" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R40" s="3">
-        <f t="shared" ref="R40:R60" si="13">R39+0.5</f>
+      <c r="S40" s="3">
+        <f t="shared" ref="S40:S60" si="13">S39+0.5</f>
         <v>7.6000000000000005</v>
       </c>
-      <c r="S40" s="3">
-        <f t="shared" ref="S40:S60" si="14">S39</f>
+      <c r="T40" s="3">
+        <f t="shared" ref="T40:T60" si="14">T39</f>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>20</v>
       </c>
@@ -2412,24 +2426,24 @@
       <c r="L41" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <f t="shared" si="8"/>
         <v>7.6000000000000005</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <f t="shared" si="13"/>
         <v>8.1000000000000014</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>20</v>
       </c>
@@ -2460,24 +2474,24 @@
       <c r="N42" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <f t="shared" si="8"/>
         <v>8.1000000000000014</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <f t="shared" si="13"/>
         <v>8.6000000000000014</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>20</v>
       </c>
@@ -2505,24 +2519,24 @@
       <c r="L43" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <f t="shared" si="8"/>
         <v>8.6000000000000014</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <f t="shared" si="13"/>
         <v>9.1000000000000014</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>20</v>
       </c>
@@ -2547,24 +2561,24 @@
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <f t="shared" si="8"/>
         <v>9.1000000000000014</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <f t="shared" si="13"/>
         <v>9.6000000000000014</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>20</v>
       </c>
@@ -2589,24 +2603,24 @@
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <f t="shared" si="8"/>
         <v>9.6000000000000014</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <f t="shared" si="13"/>
         <v>10.100000000000001</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>20</v>
       </c>
@@ -2631,24 +2645,24 @@
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <f t="shared" si="8"/>
         <v>10.100000000000001</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <f t="shared" si="13"/>
         <v>10.600000000000001</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>20</v>
       </c>
@@ -2673,24 +2687,24 @@
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <f t="shared" si="8"/>
         <v>10.600000000000001</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <f t="shared" si="13"/>
         <v>11.100000000000001</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>20</v>
       </c>
@@ -2715,24 +2729,24 @@
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <f t="shared" si="8"/>
         <v>11.100000000000001</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <f t="shared" si="13"/>
         <v>11.600000000000001</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>20</v>
       </c>
@@ -2757,24 +2771,24 @@
       <c r="I49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <f t="shared" si="8"/>
         <v>11.600000000000001</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <f t="shared" si="13"/>
         <v>12.100000000000001</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>20</v>
       </c>
@@ -2802,24 +2816,24 @@
       <c r="L50" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="P50" s="3">
+      <c r="Q50" s="3">
         <f t="shared" si="8"/>
         <v>12.100000000000001</v>
       </c>
-      <c r="Q50" s="3">
+      <c r="R50" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R50" s="3">
+      <c r="S50" s="3">
         <f t="shared" si="13"/>
         <v>12.600000000000001</v>
       </c>
-      <c r="S50" s="3">
+      <c r="T50" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>20</v>
       </c>
@@ -2850,24 +2864,24 @@
       <c r="N51" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="P51" s="3">
+      <c r="Q51" s="3">
         <f t="shared" si="8"/>
         <v>12.600000000000001</v>
       </c>
-      <c r="Q51" s="3">
+      <c r="R51" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R51" s="3">
+      <c r="S51" s="3">
         <f t="shared" si="13"/>
         <v>13.100000000000001</v>
       </c>
-      <c r="S51" s="3">
+      <c r="T51" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>20</v>
       </c>
@@ -2895,24 +2909,24 @@
       <c r="L52" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <f t="shared" si="8"/>
         <v>13.100000000000001</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <f t="shared" si="13"/>
         <v>13.600000000000001</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>20</v>
       </c>
@@ -2937,24 +2951,24 @@
       <c r="I53" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P53" s="3">
+      <c r="Q53" s="3">
         <f t="shared" si="8"/>
         <v>13.600000000000001</v>
       </c>
-      <c r="Q53" s="3">
+      <c r="R53" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R53" s="3">
+      <c r="S53" s="3">
         <f t="shared" si="13"/>
         <v>14.100000000000001</v>
       </c>
-      <c r="S53" s="3">
+      <c r="T53" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>20</v>
       </c>
@@ -2979,24 +2993,24 @@
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <f t="shared" si="8"/>
         <v>14.100000000000001</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <f t="shared" si="13"/>
         <v>14.600000000000001</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>20</v>
       </c>
@@ -3021,24 +3035,24 @@
       <c r="I55" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P55" s="3">
+      <c r="Q55" s="3">
         <f t="shared" si="8"/>
         <v>14.600000000000001</v>
       </c>
-      <c r="Q55" s="3">
+      <c r="R55" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R55" s="3">
+      <c r="S55" s="3">
         <f t="shared" si="13"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="S55" s="3">
+      <c r="T55" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>20</v>
       </c>
@@ -3063,24 +3077,24 @@
       <c r="I56" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P56" s="3">
+      <c r="Q56" s="3">
         <f t="shared" si="8"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="Q56" s="3">
+      <c r="R56" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R56" s="3">
+      <c r="S56" s="3">
         <f t="shared" si="13"/>
         <v>15.600000000000001</v>
       </c>
-      <c r="S56" s="3">
+      <c r="T56" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>20</v>
       </c>
@@ -3105,24 +3119,24 @@
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <f t="shared" si="8"/>
         <v>15.600000000000001</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <f t="shared" si="13"/>
         <v>16.100000000000001</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>20</v>
       </c>
@@ -3147,24 +3161,24 @@
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <f t="shared" si="8"/>
         <v>16.100000000000001</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <f t="shared" si="13"/>
         <v>16.600000000000001</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>20</v>
       </c>
@@ -3192,24 +3206,24 @@
       <c r="L59" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <f t="shared" si="8"/>
         <v>16.600000000000001</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <f t="shared" si="13"/>
         <v>17.100000000000001</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>20</v>
       </c>
@@ -3240,24 +3254,24 @@
       <c r="N60" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <f t="shared" si="8"/>
         <v>17.100000000000001</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <f t="shared" si="13"/>
         <v>17.600000000000001</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999998</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>20</v>
       </c>
@@ -3288,24 +3302,27 @@
       <c r="L61" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="P61" s="3">
+      <c r="P61" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q61" s="3">
         <f t="shared" si="8"/>
         <v>17.600000000000001</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <f t="shared" si="9"/>
         <v>13.599999999999998</v>
       </c>
-      <c r="R61" s="3">
-        <f>R60+1</f>
+      <c r="S61" s="3">
+        <f>S60+1</f>
         <v>18.600000000000001</v>
       </c>
-      <c r="S61" s="3">
-        <f>S60+0.8</f>
+      <c r="T61" s="3">
+        <f>T60+0.8</f>
         <v>14.399999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>20</v>
       </c>
@@ -3327,24 +3344,24 @@
       <c r="H62" s="2">
         <v>0.5</v>
       </c>
-      <c r="P62" s="3">
-        <f t="shared" ref="P62:P66" si="15">R61</f>
+      <c r="Q62" s="3">
+        <f t="shared" ref="Q62:Q66" si="15">S61</f>
         <v>18.600000000000001</v>
       </c>
-      <c r="Q62" s="3">
-        <f t="shared" ref="Q62:Q66" si="16">S61</f>
+      <c r="R62" s="3">
+        <f t="shared" ref="R62:R66" si="16">T61</f>
         <v>14.399999999999999</v>
       </c>
-      <c r="R62" s="3">
-        <f t="shared" ref="R62:R65" si="17">R61+1</f>
+      <c r="S62" s="3">
+        <f t="shared" ref="S62:S65" si="17">S61+1</f>
         <v>19.600000000000001</v>
       </c>
-      <c r="S62" s="3">
-        <f t="shared" ref="S62:S65" si="18">S61+0.8</f>
+      <c r="T62" s="3">
+        <f t="shared" ref="T62:T65" si="18">T61+0.8</f>
         <v>15.2</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>20</v>
       </c>
@@ -3366,24 +3383,24 @@
       <c r="H63" s="2">
         <v>0.5</v>
       </c>
-      <c r="P63" s="3">
+      <c r="Q63" s="3">
         <f t="shared" si="15"/>
         <v>19.600000000000001</v>
       </c>
-      <c r="Q63" s="3">
+      <c r="R63" s="3">
         <f t="shared" si="16"/>
         <v>15.2</v>
       </c>
-      <c r="R63" s="3">
+      <c r="S63" s="3">
         <f t="shared" si="17"/>
         <v>20.6</v>
       </c>
-      <c r="S63" s="3">
+      <c r="T63" s="3">
         <f t="shared" si="18"/>
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>20</v>
       </c>
@@ -3405,24 +3422,24 @@
       <c r="H64" s="2">
         <v>0.5</v>
       </c>
-      <c r="P64" s="3">
+      <c r="Q64" s="3">
         <f t="shared" si="15"/>
         <v>20.6</v>
       </c>
-      <c r="Q64" s="3">
+      <c r="R64" s="3">
         <f t="shared" si="16"/>
         <v>16</v>
       </c>
-      <c r="R64" s="3">
+      <c r="S64" s="3">
         <f t="shared" si="17"/>
         <v>21.6</v>
       </c>
-      <c r="S64" s="3">
+      <c r="T64" s="3">
         <f t="shared" si="18"/>
         <v>16.8</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>20</v>
       </c>
@@ -3450,24 +3467,27 @@
       <c r="K65" s="3">
         <v>63</v>
       </c>
-      <c r="P65" s="3">
+      <c r="P65" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q65" s="3">
         <f t="shared" si="15"/>
         <v>21.6</v>
       </c>
-      <c r="Q65" s="3">
+      <c r="R65" s="3">
         <f t="shared" si="16"/>
         <v>16.8</v>
       </c>
-      <c r="R65" s="3">
+      <c r="S65" s="3">
         <f t="shared" si="17"/>
         <v>22.6</v>
       </c>
-      <c r="S65" s="3">
+      <c r="T65" s="3">
         <f t="shared" si="18"/>
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>20</v>
       </c>
@@ -3489,24 +3509,24 @@
       <c r="H66" s="2">
         <v>0.5</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <f t="shared" si="15"/>
         <v>22.6</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <f t="shared" si="16"/>
         <v>17.600000000000001</v>
       </c>
-      <c r="R66" s="3">
-        <f>R65</f>
+      <c r="S66" s="3">
+        <f>S65</f>
         <v>22.6</v>
       </c>
-      <c r="S66" s="3">
-        <f>S65+1</f>
+      <c r="T66" s="3">
+        <f>T65+1</f>
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>20</v>
       </c>
@@ -3531,24 +3551,24 @@
       <c r="L67" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="P67" s="3">
-        <f t="shared" ref="P67:P130" si="19">R66</f>
+      <c r="Q67" s="3">
+        <f t="shared" ref="Q67:Q130" si="19">S66</f>
         <v>22.6</v>
       </c>
-      <c r="Q67" s="3">
-        <f t="shared" ref="Q67:Q130" si="20">S66</f>
+      <c r="R67" s="3">
+        <f t="shared" ref="R67:R130" si="20">T66</f>
         <v>18.600000000000001</v>
       </c>
-      <c r="R67" s="3">
-        <f t="shared" ref="R67:R71" si="21">R66</f>
+      <c r="S67" s="3">
+        <f t="shared" ref="S67:S71" si="21">S66</f>
         <v>22.6</v>
       </c>
-      <c r="S67" s="3">
-        <f>S66+1</f>
+      <c r="T67" s="3">
+        <f>T66+1</f>
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>20</v>
       </c>
@@ -3576,24 +3596,24 @@
       <c r="N68" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="P68" s="3">
+      <c r="Q68" s="3">
         <f t="shared" si="19"/>
         <v>22.6</v>
       </c>
-      <c r="Q68" s="3">
+      <c r="R68" s="3">
         <f t="shared" si="20"/>
         <v>19.600000000000001</v>
       </c>
-      <c r="R68" s="3">
+      <c r="S68" s="3">
         <f t="shared" si="21"/>
         <v>22.6</v>
       </c>
-      <c r="S68" s="3">
-        <f>S65+4.2</f>
+      <c r="T68" s="3">
+        <f>T65+4.2</f>
         <v>21.8</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>20</v>
       </c>
@@ -3618,24 +3638,24 @@
       <c r="L69" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="P69" s="3">
+      <c r="Q69" s="3">
         <f t="shared" si="19"/>
         <v>22.6</v>
       </c>
-      <c r="Q69" s="3">
+      <c r="R69" s="3">
         <f t="shared" si="20"/>
         <v>21.8</v>
       </c>
-      <c r="R69" s="3">
+      <c r="S69" s="3">
         <f t="shared" si="21"/>
         <v>22.6</v>
       </c>
-      <c r="S69" s="3">
-        <f>S68+2.2</f>
+      <c r="T69" s="3">
+        <f>T68+2.2</f>
         <v>24</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>20</v>
       </c>
@@ -3657,24 +3677,24 @@
       <c r="H70" s="2">
         <v>0.5</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <f t="shared" si="19"/>
         <v>22.6</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <f t="shared" si="20"/>
         <v>24</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <f t="shared" si="21"/>
         <v>22.6</v>
       </c>
-      <c r="S70" s="3">
-        <f>S69+1</f>
+      <c r="T70" s="3">
+        <f>T69+1</f>
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>20</v>
       </c>
@@ -3696,24 +3716,24 @@
       <c r="H71" s="2">
         <v>0.5</v>
       </c>
-      <c r="P71" s="3">
+      <c r="Q71" s="3">
         <f t="shared" si="19"/>
         <v>22.6</v>
       </c>
-      <c r="Q71" s="3">
+      <c r="R71" s="3">
         <f t="shared" si="20"/>
         <v>25</v>
       </c>
-      <c r="R71" s="3">
+      <c r="S71" s="3">
         <f t="shared" si="21"/>
         <v>22.6</v>
       </c>
-      <c r="S71" s="3">
-        <f>S68+4.2</f>
+      <c r="T71" s="3">
+        <f>T68+4.2</f>
         <v>26</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>20</v>
       </c>
@@ -3735,24 +3755,24 @@
       <c r="H72" s="2">
         <v>0.5</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <f t="shared" si="19"/>
         <v>22.6</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <f t="shared" si="20"/>
         <v>26</v>
       </c>
-      <c r="R72" s="3">
-        <f>R71-0.7</f>
+      <c r="S72" s="3">
+        <f>S71-0.7</f>
         <v>21.900000000000002</v>
       </c>
-      <c r="S72" s="3">
-        <f>S71+1</f>
+      <c r="T72" s="3">
+        <f>T71+1</f>
         <v>27</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>20</v>
       </c>
@@ -3774,24 +3794,24 @@
       <c r="H73" s="2">
         <v>0.5</v>
       </c>
-      <c r="P73" s="3">
+      <c r="Q73" s="3">
         <f t="shared" si="19"/>
         <v>21.900000000000002</v>
       </c>
-      <c r="Q73" s="3">
+      <c r="R73" s="3">
         <f t="shared" si="20"/>
         <v>27</v>
       </c>
-      <c r="R73" s="3">
-        <f t="shared" ref="R73:R76" si="22">R72-0.7</f>
+      <c r="S73" s="3">
+        <f t="shared" ref="S73:S76" si="22">S72-0.7</f>
         <v>21.200000000000003</v>
       </c>
-      <c r="S73" s="3">
-        <f t="shared" ref="S73:S76" si="23">S72+1</f>
+      <c r="T73" s="3">
+        <f t="shared" ref="T73:T76" si="23">T72+1</f>
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>20</v>
       </c>
@@ -3813,24 +3833,24 @@
       <c r="H74" s="2">
         <v>0.5</v>
       </c>
-      <c r="P74" s="3">
+      <c r="Q74" s="3">
         <f t="shared" si="19"/>
         <v>21.200000000000003</v>
       </c>
-      <c r="Q74" s="3">
+      <c r="R74" s="3">
         <f t="shared" si="20"/>
         <v>28</v>
       </c>
-      <c r="R74" s="3">
+      <c r="S74" s="3">
         <f t="shared" si="22"/>
         <v>20.500000000000004</v>
       </c>
-      <c r="S74" s="3">
+      <c r="T74" s="3">
         <f t="shared" si="23"/>
         <v>29</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>20</v>
       </c>
@@ -3855,24 +3875,24 @@
       <c r="L75" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="P75" s="3">
+      <c r="Q75" s="3">
         <f t="shared" si="19"/>
         <v>20.500000000000004</v>
       </c>
-      <c r="Q75" s="3">
+      <c r="R75" s="3">
         <f t="shared" si="20"/>
         <v>29</v>
       </c>
-      <c r="R75" s="3">
+      <c r="S75" s="3">
         <f t="shared" si="22"/>
         <v>19.800000000000004</v>
       </c>
-      <c r="S75" s="3">
+      <c r="T75" s="3">
         <f t="shared" si="23"/>
         <v>30</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>20</v>
       </c>
@@ -3900,24 +3920,24 @@
       <c r="N76" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <f t="shared" si="19"/>
         <v>19.800000000000004</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <f t="shared" si="20"/>
         <v>30</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <f t="shared" si="22"/>
         <v>19.100000000000005</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <f t="shared" si="23"/>
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>20</v>
       </c>
@@ -3945,24 +3965,24 @@
       <c r="L77" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="P77" s="3">
+      <c r="Q77" s="3">
         <f t="shared" si="19"/>
         <v>19.100000000000005</v>
       </c>
-      <c r="Q77" s="3">
+      <c r="R77" s="3">
         <f t="shared" si="20"/>
         <v>31</v>
       </c>
-      <c r="R77" s="3">
-        <f>R76-2.2</f>
+      <c r="S77" s="3">
+        <f>S76-2.2</f>
         <v>16.900000000000006</v>
       </c>
-      <c r="S77" s="3">
-        <f>S76</f>
+      <c r="T77" s="3">
+        <f>T76</f>
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>20</v>
       </c>
@@ -3987,24 +4007,24 @@
       <c r="H78" s="2">
         <v>0.5</v>
       </c>
-      <c r="P78" s="3">
+      <c r="Q78" s="3">
         <f t="shared" si="19"/>
         <v>16.900000000000006</v>
       </c>
-      <c r="Q78" s="3">
+      <c r="R78" s="3">
         <f t="shared" si="20"/>
         <v>31</v>
       </c>
-      <c r="R78" s="3">
-        <f t="shared" ref="R78:R79" si="24">R77-2.2</f>
+      <c r="S78" s="3">
+        <f t="shared" ref="S78:S79" si="24">S77-2.2</f>
         <v>14.700000000000006</v>
       </c>
-      <c r="S78" s="3">
-        <f t="shared" ref="S78:S79" si="25">S77</f>
+      <c r="T78" s="3">
+        <f t="shared" ref="T78:T79" si="25">T77</f>
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>20</v>
       </c>
@@ -4032,24 +4052,24 @@
       <c r="L79" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="P79" s="3">
+      <c r="Q79" s="3">
         <f t="shared" si="19"/>
         <v>14.700000000000006</v>
       </c>
-      <c r="Q79" s="3">
+      <c r="R79" s="3">
         <f t="shared" si="20"/>
         <v>31</v>
       </c>
-      <c r="R79" s="3">
+      <c r="S79" s="3">
         <f t="shared" si="24"/>
         <v>12.500000000000007</v>
       </c>
-      <c r="S79" s="3">
+      <c r="T79" s="3">
         <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>20</v>
       </c>
@@ -4086,24 +4106,27 @@
       <c r="N80" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P80" s="3">
+      <c r="P80" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="3">
         <f t="shared" si="19"/>
         <v>12.500000000000007</v>
       </c>
-      <c r="Q80" s="3">
+      <c r="R80" s="3">
         <f t="shared" si="20"/>
         <v>31</v>
       </c>
-      <c r="R80" s="3">
-        <f>R79-0.6</f>
+      <c r="S80" s="3">
+        <f>S79-0.6</f>
         <v>11.900000000000007</v>
       </c>
-      <c r="S80" s="3">
-        <f>S79</f>
+      <c r="T80" s="3">
+        <f>T79</f>
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>20</v>
       </c>
@@ -4131,24 +4154,24 @@
       <c r="L81" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <f t="shared" si="19"/>
         <v>11.900000000000007</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <f t="shared" si="20"/>
         <v>31</v>
       </c>
-      <c r="R81" s="3">
-        <f t="shared" ref="R81:R87" si="26">R80-0.6</f>
+      <c r="S81" s="3">
+        <f t="shared" ref="S81:S87" si="26">S80-0.6</f>
         <v>11.300000000000008</v>
       </c>
-      <c r="S81" s="3">
-        <f t="shared" ref="S81:S88" si="27">S80</f>
+      <c r="T81" s="3">
+        <f t="shared" ref="T81:T88" si="27">T80</f>
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>20</v>
       </c>
@@ -4173,24 +4196,24 @@
       <c r="H82" s="2">
         <v>0.5</v>
       </c>
-      <c r="P82" s="3">
+      <c r="Q82" s="3">
         <f t="shared" si="19"/>
         <v>11.300000000000008</v>
       </c>
-      <c r="Q82" s="3">
+      <c r="R82" s="3">
         <f t="shared" si="20"/>
         <v>31</v>
       </c>
-      <c r="R82" s="3">
+      <c r="S82" s="3">
         <f t="shared" si="26"/>
         <v>10.700000000000008</v>
       </c>
-      <c r="S82" s="3">
+      <c r="T82" s="3">
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>20</v>
       </c>
@@ -4215,24 +4238,24 @@
       <c r="H83" s="2">
         <v>0.5</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <f t="shared" si="19"/>
         <v>10.700000000000008</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <f t="shared" si="20"/>
         <v>31</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <f t="shared" si="26"/>
         <v>10.100000000000009</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>20</v>
       </c>
@@ -4257,24 +4280,24 @@
       <c r="H84" s="2">
         <v>0.5</v>
       </c>
-      <c r="P84" s="3">
+      <c r="Q84" s="3">
         <f t="shared" si="19"/>
         <v>10.100000000000009</v>
       </c>
-      <c r="Q84" s="3">
+      <c r="R84" s="3">
         <f t="shared" si="20"/>
         <v>31</v>
       </c>
-      <c r="R84" s="3">
+      <c r="S84" s="3">
         <f t="shared" si="26"/>
         <v>9.5000000000000089</v>
       </c>
-      <c r="S84" s="3">
+      <c r="T84" s="3">
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>20</v>
       </c>
@@ -4299,24 +4322,24 @@
       <c r="H85" s="2">
         <v>0.5</v>
       </c>
-      <c r="P85" s="3">
+      <c r="Q85" s="3">
         <f t="shared" si="19"/>
         <v>9.5000000000000089</v>
       </c>
-      <c r="Q85" s="3">
+      <c r="R85" s="3">
         <f t="shared" si="20"/>
         <v>31</v>
       </c>
-      <c r="R85" s="3">
+      <c r="S85" s="3">
         <f t="shared" si="26"/>
         <v>8.9000000000000092</v>
       </c>
-      <c r="S85" s="3">
+      <c r="T85" s="3">
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>20</v>
       </c>
@@ -4341,24 +4364,24 @@
       <c r="H86" s="2">
         <v>0.5</v>
       </c>
-      <c r="P86" s="3">
+      <c r="Q86" s="3">
         <f t="shared" si="19"/>
         <v>8.9000000000000092</v>
       </c>
-      <c r="Q86" s="3">
+      <c r="R86" s="3">
         <f t="shared" si="20"/>
         <v>31</v>
       </c>
-      <c r="R86" s="3">
+      <c r="S86" s="3">
         <f t="shared" si="26"/>
         <v>8.3000000000000096</v>
       </c>
-      <c r="S86" s="3">
+      <c r="T86" s="3">
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>20</v>
       </c>
@@ -4383,24 +4406,24 @@
       <c r="H87" s="2">
         <v>0.5</v>
       </c>
-      <c r="P87" s="3">
+      <c r="Q87" s="3">
         <f t="shared" si="19"/>
         <v>8.3000000000000096</v>
       </c>
-      <c r="Q87" s="3">
+      <c r="R87" s="3">
         <f t="shared" si="20"/>
         <v>31</v>
       </c>
-      <c r="R87" s="3">
+      <c r="S87" s="3">
         <f t="shared" si="26"/>
         <v>7.7000000000000099</v>
       </c>
-      <c r="S87" s="3">
+      <c r="T87" s="3">
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>20</v>
       </c>
@@ -4431,24 +4454,27 @@
       <c r="K88" s="3">
         <v>100</v>
       </c>
-      <c r="P88" s="3">
+      <c r="P88" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q88" s="3">
         <f t="shared" si="19"/>
         <v>7.7000000000000099</v>
       </c>
-      <c r="Q88" s="3">
+      <c r="R88" s="3">
         <f t="shared" si="20"/>
         <v>31</v>
       </c>
-      <c r="R88" s="3">
-        <f>R87-0.6</f>
+      <c r="S88" s="3">
+        <f>S87-0.6</f>
         <v>7.1000000000000103</v>
       </c>
-      <c r="S88" s="3">
+      <c r="T88" s="3">
         <f t="shared" si="27"/>
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>20</v>
       </c>
@@ -4473,24 +4499,24 @@
       <c r="H89" s="2">
         <v>0.5</v>
       </c>
-      <c r="P89" s="3">
-        <f>R88</f>
+      <c r="Q89" s="3">
+        <f>S88</f>
         <v>7.1000000000000103</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <f t="shared" si="20"/>
         <v>31</v>
       </c>
-      <c r="R89" s="3">
-        <f>R88-1.2</f>
+      <c r="S89" s="3">
+        <f>S88-1.2</f>
         <v>5.9000000000000101</v>
       </c>
-      <c r="S89" s="3">
-        <f>S88</f>
+      <c r="T89" s="3">
+        <f>T88</f>
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>20</v>
       </c>
@@ -4518,24 +4544,24 @@
       <c r="L90" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="P90" s="3">
-        <f>R89</f>
+      <c r="Q90" s="3">
+        <f>S89</f>
         <v>5.9000000000000101</v>
       </c>
-      <c r="Q90" s="3">
+      <c r="R90" s="3">
         <f t="shared" si="20"/>
         <v>31</v>
       </c>
-      <c r="R90" s="3">
-        <f t="shared" ref="R90:R91" si="28">R89-1.2</f>
+      <c r="S90" s="3">
+        <f t="shared" ref="S90:S91" si="28">S89-1.2</f>
         <v>4.7000000000000099</v>
       </c>
-      <c r="S90" s="3">
-        <f t="shared" ref="S90:S91" si="29">S89</f>
+      <c r="T90" s="3">
+        <f t="shared" ref="T90:T91" si="29">T89</f>
         <v>31</v>
       </c>
     </row>
-    <row r="91" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>20</v>
       </c>
@@ -4566,24 +4592,24 @@
       <c r="N91" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <f t="shared" si="19"/>
         <v>4.7000000000000099</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <f t="shared" si="20"/>
         <v>31</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <f t="shared" si="28"/>
         <v>3.5000000000000098</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <f t="shared" si="29"/>
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>20</v>
       </c>
@@ -4608,24 +4634,24 @@
       <c r="L92" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="P92" s="3">
+      <c r="Q92" s="3">
         <f t="shared" si="19"/>
         <v>3.5000000000000098</v>
       </c>
-      <c r="Q92" s="3">
+      <c r="R92" s="3">
         <f t="shared" si="20"/>
         <v>31</v>
       </c>
-      <c r="R92" s="3">
-        <f>R91-0.5</f>
+      <c r="S92" s="3">
+        <f>S91-0.5</f>
         <v>3.0000000000000098</v>
       </c>
-      <c r="S92" s="3">
-        <f>S91-0.8</f>
+      <c r="T92" s="3">
+        <f>T91-0.8</f>
         <v>30.2</v>
       </c>
     </row>
-    <row r="93" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>20</v>
       </c>
@@ -4647,24 +4673,24 @@
       <c r="H93" s="2">
         <v>-0.625</v>
       </c>
-      <c r="P93" s="3">
+      <c r="Q93" s="3">
         <f t="shared" si="19"/>
         <v>3.0000000000000098</v>
       </c>
-      <c r="Q93" s="3">
+      <c r="R93" s="3">
         <f t="shared" si="20"/>
         <v>30.2</v>
       </c>
-      <c r="R93" s="3">
-        <f t="shared" ref="R93:R94" si="30">R92-0.5</f>
+      <c r="S93" s="3">
+        <f t="shared" ref="S93:S94" si="30">S92-0.5</f>
         <v>2.5000000000000098</v>
       </c>
-      <c r="S93" s="3">
-        <f t="shared" ref="S93:S97" si="31">S92-0.8</f>
+      <c r="T93" s="3">
+        <f t="shared" ref="T93:T97" si="31">T92-0.8</f>
         <v>29.4</v>
       </c>
     </row>
-    <row r="94" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>20</v>
       </c>
@@ -4686,24 +4712,24 @@
       <c r="H94" s="2">
         <v>-2.125</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <f t="shared" si="19"/>
         <v>2.5000000000000098</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <f t="shared" si="20"/>
         <v>29.4</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <f t="shared" si="30"/>
         <v>2.0000000000000098</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <f t="shared" si="31"/>
         <v>28.599999999999998</v>
       </c>
     </row>
-    <row r="95" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>20</v>
       </c>
@@ -4725,24 +4751,24 @@
       <c r="H95" s="2">
         <v>-2.125</v>
       </c>
-      <c r="P95" s="3">
+      <c r="Q95" s="3">
         <f t="shared" si="19"/>
         <v>2.0000000000000098</v>
       </c>
-      <c r="Q95" s="3">
+      <c r="R95" s="3">
         <f t="shared" si="20"/>
         <v>28.599999999999998</v>
       </c>
-      <c r="R95" s="3">
-        <f>R94+0.5</f>
+      <c r="S95" s="3">
+        <f>S94+0.5</f>
         <v>2.5000000000000098</v>
       </c>
-      <c r="S95" s="3">
+      <c r="T95" s="3">
         <f t="shared" si="31"/>
         <v>27.799999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>20</v>
       </c>
@@ -4764,24 +4790,24 @@
       <c r="H96" s="2">
         <v>-0.625</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <f t="shared" si="19"/>
         <v>2.5000000000000098</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <f t="shared" si="20"/>
         <v>27.799999999999997</v>
       </c>
-      <c r="R96" s="3">
-        <f t="shared" ref="R96:R100" si="32">R95+0.5</f>
+      <c r="S96" s="3">
+        <f t="shared" ref="S96:S100" si="32">S95+0.5</f>
         <v>3.0000000000000098</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <f t="shared" si="31"/>
         <v>26.999999999999996</v>
       </c>
     </row>
-    <row r="97" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>20</v>
       </c>
@@ -4803,24 +4829,24 @@
       <c r="H97" s="2">
         <v>0.125</v>
       </c>
-      <c r="P97" s="3">
+      <c r="Q97" s="3">
         <f t="shared" si="19"/>
         <v>3.0000000000000098</v>
       </c>
-      <c r="Q97" s="3">
+      <c r="R97" s="3">
         <f t="shared" si="20"/>
         <v>26.999999999999996</v>
       </c>
-      <c r="R97" s="3">
+      <c r="S97" s="3">
         <f t="shared" si="32"/>
         <v>3.5000000000000098</v>
       </c>
-      <c r="S97" s="3">
+      <c r="T97" s="3">
         <f t="shared" si="31"/>
         <v>26.199999999999996</v>
       </c>
     </row>
-    <row r="98" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>20</v>
       </c>
@@ -4845,24 +4871,24 @@
       <c r="L98" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="P98" s="3">
+      <c r="Q98" s="3">
         <f t="shared" si="19"/>
         <v>3.5000000000000098</v>
       </c>
-      <c r="Q98" s="3">
+      <c r="R98" s="3">
         <f t="shared" si="20"/>
         <v>26.199999999999996</v>
       </c>
-      <c r="R98" s="3">
+      <c r="S98" s="3">
         <f t="shared" si="32"/>
         <v>4.0000000000000098</v>
       </c>
-      <c r="S98" s="3">
-        <f>S97+0.8</f>
+      <c r="T98" s="3">
+        <f>T97+0.8</f>
         <v>26.999999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>20</v>
       </c>
@@ -4890,24 +4916,24 @@
       <c r="N99" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="P99" s="3">
+      <c r="Q99" s="3">
         <f t="shared" si="19"/>
         <v>4.0000000000000098</v>
       </c>
-      <c r="Q99" s="3">
+      <c r="R99" s="3">
         <f t="shared" si="20"/>
         <v>26.999999999999996</v>
       </c>
-      <c r="R99" s="3">
+      <c r="S99" s="3">
         <f t="shared" si="32"/>
         <v>4.5000000000000098</v>
       </c>
-      <c r="S99" s="3">
-        <f t="shared" ref="S99:S100" si="33">S98+0.8</f>
+      <c r="T99" s="3">
+        <f t="shared" ref="T99:T100" si="33">T98+0.8</f>
         <v>27.799999999999997</v>
       </c>
     </row>
-    <row r="100" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>20</v>
       </c>
@@ -4932,24 +4958,24 @@
       <c r="L100" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <f t="shared" si="19"/>
         <v>4.5000000000000098</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <f t="shared" si="20"/>
         <v>27.799999999999997</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <f t="shared" si="32"/>
         <v>5.0000000000000098</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <f t="shared" si="33"/>
         <v>28.599999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>20</v>
       </c>
@@ -4971,24 +4997,24 @@
       <c r="H101" s="2">
         <v>0.5</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <f t="shared" si="19"/>
         <v>5.0000000000000098</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <f t="shared" si="20"/>
         <v>28.599999999999998</v>
       </c>
-      <c r="R101" s="3">
-        <f>R100+0.7</f>
+      <c r="S101" s="3">
+        <f>S100+0.7</f>
         <v>5.7000000000000099</v>
       </c>
-      <c r="S101" s="3">
-        <f>S100+0.8</f>
+      <c r="T101" s="3">
+        <f>T100+0.8</f>
         <v>29.4</v>
       </c>
     </row>
-    <row r="102" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>20</v>
       </c>
@@ -5010,24 +5036,24 @@
       <c r="H102" s="2">
         <v>0.5</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <f t="shared" si="19"/>
         <v>5.7000000000000099</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <f t="shared" si="20"/>
         <v>29.4</v>
       </c>
-      <c r="R102" s="3">
-        <f t="shared" ref="R102:R103" si="34">R101+0.7</f>
+      <c r="S102" s="3">
+        <f t="shared" ref="S102:S103" si="34">S101+0.7</f>
         <v>6.4000000000000101</v>
       </c>
-      <c r="S102" s="3">
-        <f t="shared" ref="S102:S103" si="35">S101+0.8</f>
+      <c r="T102" s="3">
+        <f t="shared" ref="T102:T103" si="35">T101+0.8</f>
         <v>30.2</v>
       </c>
     </row>
-    <row r="103" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>20</v>
       </c>
@@ -5049,24 +5075,24 @@
       <c r="H103" s="2">
         <v>0.5</v>
       </c>
-      <c r="P103" s="3">
+      <c r="Q103" s="3">
         <f t="shared" si="19"/>
         <v>6.4000000000000101</v>
       </c>
-      <c r="Q103" s="3">
+      <c r="R103" s="3">
         <f t="shared" si="20"/>
         <v>30.2</v>
       </c>
-      <c r="R103" s="3">
+      <c r="S103" s="3">
         <f t="shared" si="34"/>
         <v>7.1000000000000103</v>
       </c>
-      <c r="S103" s="3">
+      <c r="T103" s="3">
         <f t="shared" si="35"/>
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>20</v>
       </c>
@@ -5088,20 +5114,20 @@
       <c r="H104" s="2">
         <v>0.5</v>
       </c>
-      <c r="P104" s="3">
+      <c r="Q104" s="3">
         <v>12.500000000000007</v>
       </c>
-      <c r="Q104" s="3">
+      <c r="R104" s="3">
         <v>31</v>
       </c>
-      <c r="R104" s="3">
+      <c r="S104" s="3">
         <v>14</v>
       </c>
-      <c r="S104" s="3">
+      <c r="T104" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="105" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>20</v>
       </c>
@@ -5123,22 +5149,22 @@
       <c r="H105" s="2">
         <v>0.5</v>
       </c>
-      <c r="P105" s="3">
+      <c r="Q105" s="3">
         <f t="shared" si="19"/>
         <v>14</v>
       </c>
-      <c r="Q105" s="3">
+      <c r="R105" s="3">
         <f t="shared" si="20"/>
         <v>29</v>
       </c>
-      <c r="R105" s="3">
+      <c r="S105" s="3">
         <v>15</v>
       </c>
-      <c r="S105" s="3">
+      <c r="T105" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="106" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>20</v>
       </c>
@@ -5160,22 +5186,22 @@
       <c r="H106" s="2">
         <v>0.5</v>
       </c>
-      <c r="P106" s="3">
+      <c r="Q106" s="3">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="Q106" s="3">
+      <c r="R106" s="3">
         <f t="shared" si="20"/>
         <v>29</v>
       </c>
-      <c r="R106" s="3">
+      <c r="S106" s="3">
         <v>16</v>
       </c>
-      <c r="S106" s="3">
+      <c r="T106" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="107" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>20</v>
       </c>
@@ -5200,22 +5226,22 @@
       <c r="L107" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="P107" s="3">
+      <c r="Q107" s="3">
         <f t="shared" si="19"/>
         <v>16</v>
       </c>
-      <c r="Q107" s="3">
+      <c r="R107" s="3">
         <f t="shared" si="20"/>
         <v>29</v>
       </c>
-      <c r="R107" s="3">
+      <c r="S107" s="3">
         <v>17</v>
       </c>
-      <c r="S107" s="3">
+      <c r="T107" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="108" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>20</v>
       </c>
@@ -5243,24 +5269,24 @@
       <c r="N108" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="P108" s="3">
+      <c r="Q108" s="3">
         <f t="shared" si="19"/>
         <v>17</v>
       </c>
-      <c r="Q108" s="3">
+      <c r="R108" s="3">
         <f t="shared" si="20"/>
         <v>29</v>
       </c>
-      <c r="R108" s="3">
-        <f>R107+0.8</f>
+      <c r="S108" s="3">
+        <f>S107+0.8</f>
         <v>17.8</v>
       </c>
-      <c r="S108" s="3">
-        <f>S107-1</f>
+      <c r="T108" s="3">
+        <f>T107-1</f>
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>20</v>
       </c>
@@ -5285,24 +5311,24 @@
       <c r="L109" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="P109" s="3">
+      <c r="Q109" s="3">
         <f t="shared" si="19"/>
         <v>17.8</v>
       </c>
-      <c r="Q109" s="3">
+      <c r="R109" s="3">
         <f t="shared" si="20"/>
         <v>28</v>
       </c>
-      <c r="R109" s="3">
-        <f t="shared" ref="R109:R112" si="36">R108+0.8</f>
+      <c r="S109" s="3">
+        <f t="shared" ref="S109:S112" si="36">S108+0.8</f>
         <v>18.600000000000001</v>
       </c>
-      <c r="S109" s="3">
-        <f t="shared" ref="S109:S112" si="37">S108-1</f>
+      <c r="T109" s="3">
+        <f t="shared" ref="T109:T112" si="37">T108-1</f>
         <v>27</v>
       </c>
     </row>
-    <row r="110" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>20</v>
       </c>
@@ -5324,24 +5350,24 @@
       <c r="H110" s="2">
         <v>0.5</v>
       </c>
-      <c r="P110" s="3">
+      <c r="Q110" s="3">
         <f t="shared" si="19"/>
         <v>18.600000000000001</v>
       </c>
-      <c r="Q110" s="3">
+      <c r="R110" s="3">
         <f t="shared" si="20"/>
         <v>27</v>
       </c>
-      <c r="R110" s="3">
+      <c r="S110" s="3">
         <f t="shared" si="36"/>
         <v>19.400000000000002</v>
       </c>
-      <c r="S110" s="3">
+      <c r="T110" s="3">
         <f t="shared" si="37"/>
         <v>26</v>
       </c>
     </row>
-    <row r="111" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>20</v>
       </c>
@@ -5366,24 +5392,24 @@
       <c r="O111" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P111" s="3">
+      <c r="Q111" s="3">
         <f t="shared" si="19"/>
         <v>19.400000000000002</v>
       </c>
-      <c r="Q111" s="3">
+      <c r="R111" s="3">
         <f t="shared" si="20"/>
         <v>26</v>
       </c>
-      <c r="R111" s="3">
+      <c r="S111" s="3">
         <f t="shared" si="36"/>
         <v>20.200000000000003</v>
       </c>
-      <c r="S111" s="3">
+      <c r="T111" s="3">
         <f t="shared" si="37"/>
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>20</v>
       </c>
@@ -5405,24 +5431,24 @@
       <c r="H112" s="2">
         <v>0.5</v>
       </c>
-      <c r="P112" s="3">
+      <c r="Q112" s="3">
         <f t="shared" si="19"/>
         <v>20.200000000000003</v>
       </c>
-      <c r="Q112" s="3">
+      <c r="R112" s="3">
         <f t="shared" si="20"/>
         <v>25</v>
       </c>
-      <c r="R112" s="3">
+      <c r="S112" s="3">
         <f t="shared" si="36"/>
         <v>21.000000000000004</v>
       </c>
-      <c r="S112" s="3">
+      <c r="T112" s="3">
         <f t="shared" si="37"/>
         <v>24</v>
       </c>
     </row>
-    <row r="113" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>20</v>
       </c>
@@ -5444,24 +5470,24 @@
       <c r="H113" s="2">
         <v>0.5</v>
       </c>
-      <c r="P113" s="3">
+      <c r="Q113" s="3">
         <f t="shared" si="19"/>
         <v>21.000000000000004</v>
       </c>
-      <c r="Q113" s="3">
+      <c r="R113" s="3">
         <f t="shared" si="20"/>
         <v>24</v>
       </c>
-      <c r="R113" s="3">
-        <f>R112</f>
+      <c r="S113" s="3">
+        <f>S112</f>
         <v>21.000000000000004</v>
       </c>
-      <c r="S113" s="3">
-        <f>S112-0.7</f>
+      <c r="T113" s="3">
+        <f>T112-0.7</f>
         <v>23.3</v>
       </c>
     </row>
-    <row r="114" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>20</v>
       </c>
@@ -5483,24 +5509,24 @@
       <c r="H114" s="2">
         <v>0.5</v>
       </c>
-      <c r="P114" s="3">
+      <c r="Q114" s="3">
         <f t="shared" si="19"/>
         <v>21.000000000000004</v>
       </c>
-      <c r="Q114" s="3">
+      <c r="R114" s="3">
         <f t="shared" si="20"/>
         <v>23.3</v>
       </c>
-      <c r="R114" s="3">
-        <f t="shared" ref="R114:R119" si="38">R113</f>
+      <c r="S114" s="3">
+        <f t="shared" ref="S114:S119" si="38">S113</f>
         <v>21.000000000000004</v>
       </c>
-      <c r="S114" s="3">
-        <f t="shared" ref="S114:S119" si="39">S113-0.7</f>
+      <c r="T114" s="3">
+        <f t="shared" ref="T114:T119" si="39">T113-0.7</f>
         <v>22.6</v>
       </c>
     </row>
-    <row r="115" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>20</v>
       </c>
@@ -5522,24 +5548,24 @@
       <c r="H115" s="2">
         <v>0.5</v>
       </c>
-      <c r="P115" s="3">
+      <c r="Q115" s="3">
         <f t="shared" si="19"/>
         <v>21.000000000000004</v>
       </c>
-      <c r="Q115" s="3">
+      <c r="R115" s="3">
         <f t="shared" si="20"/>
         <v>22.6</v>
       </c>
-      <c r="R115" s="3">
+      <c r="S115" s="3">
         <f t="shared" si="38"/>
         <v>21.000000000000004</v>
       </c>
-      <c r="S115" s="3">
+      <c r="T115" s="3">
         <f t="shared" si="39"/>
         <v>21.900000000000002</v>
       </c>
     </row>
-    <row r="116" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>20</v>
       </c>
@@ -5564,24 +5590,24 @@
       <c r="L116" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="P116" s="3">
+      <c r="Q116" s="3">
         <f t="shared" si="19"/>
         <v>21.000000000000004</v>
       </c>
-      <c r="Q116" s="3">
+      <c r="R116" s="3">
         <f t="shared" si="20"/>
         <v>21.900000000000002</v>
       </c>
-      <c r="R116" s="3">
+      <c r="S116" s="3">
         <f t="shared" si="38"/>
         <v>21.000000000000004</v>
       </c>
-      <c r="S116" s="3">
+      <c r="T116" s="3">
         <f t="shared" si="39"/>
         <v>21.200000000000003</v>
       </c>
     </row>
-    <row r="117" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>20</v>
       </c>
@@ -5609,24 +5635,24 @@
       <c r="N117" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="P117" s="3">
+      <c r="Q117" s="3">
         <f t="shared" si="19"/>
         <v>21.000000000000004</v>
       </c>
-      <c r="Q117" s="3">
+      <c r="R117" s="3">
         <f t="shared" si="20"/>
         <v>21.200000000000003</v>
       </c>
-      <c r="R117" s="3">
+      <c r="S117" s="3">
         <f t="shared" si="38"/>
         <v>21.000000000000004</v>
       </c>
-      <c r="S117" s="3">
+      <c r="T117" s="3">
         <f t="shared" si="39"/>
         <v>20.500000000000004</v>
       </c>
     </row>
-    <row r="118" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>20</v>
       </c>
@@ -5651,24 +5677,24 @@
       <c r="L118" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="P118" s="3">
+      <c r="Q118" s="3">
         <f t="shared" si="19"/>
         <v>21.000000000000004</v>
       </c>
-      <c r="Q118" s="3">
+      <c r="R118" s="3">
         <f t="shared" si="20"/>
         <v>20.500000000000004</v>
       </c>
-      <c r="R118" s="3">
+      <c r="S118" s="3">
         <f t="shared" si="38"/>
         <v>21.000000000000004</v>
       </c>
-      <c r="S118" s="3">
+      <c r="T118" s="3">
         <f t="shared" si="39"/>
         <v>19.800000000000004</v>
       </c>
     </row>
-    <row r="119" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>20</v>
       </c>
@@ -5690,24 +5716,24 @@
       <c r="H119" s="2">
         <v>0.5</v>
       </c>
-      <c r="P119" s="3">
+      <c r="Q119" s="3">
         <f t="shared" si="19"/>
         <v>21.000000000000004</v>
       </c>
-      <c r="Q119" s="3">
+      <c r="R119" s="3">
         <f t="shared" si="20"/>
         <v>19.800000000000004</v>
       </c>
-      <c r="R119" s="3">
+      <c r="S119" s="3">
         <f t="shared" si="38"/>
         <v>21.000000000000004</v>
       </c>
-      <c r="S119" s="3">
+      <c r="T119" s="3">
         <f t="shared" si="39"/>
         <v>19.100000000000005</v>
       </c>
     </row>
-    <row r="120" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>20</v>
       </c>
@@ -5729,24 +5755,24 @@
       <c r="H120" s="2">
         <v>0.5</v>
       </c>
-      <c r="P120" s="3">
+      <c r="Q120" s="3">
         <f t="shared" si="19"/>
         <v>21.000000000000004</v>
       </c>
-      <c r="Q120" s="3">
+      <c r="R120" s="3">
         <f t="shared" si="20"/>
         <v>19.100000000000005</v>
       </c>
-      <c r="R120" s="3">
-        <f>R119-0.9</f>
+      <c r="S120" s="3">
+        <f>S119-0.9</f>
         <v>20.100000000000005</v>
       </c>
-      <c r="S120" s="3">
-        <f>S119-0.8</f>
+      <c r="T120" s="3">
+        <f>T119-0.8</f>
         <v>18.300000000000004</v>
       </c>
     </row>
-    <row r="121" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>20</v>
       </c>
@@ -5768,24 +5794,24 @@
       <c r="H121" s="2">
         <v>0.5</v>
       </c>
-      <c r="P121" s="3">
+      <c r="Q121" s="3">
         <f t="shared" si="19"/>
         <v>20.100000000000005</v>
       </c>
-      <c r="Q121" s="3">
+      <c r="R121" s="3">
         <f t="shared" si="20"/>
         <v>18.300000000000004</v>
       </c>
-      <c r="R121" s="3">
-        <f>R120-0.9</f>
+      <c r="S121" s="3">
+        <f>S120-0.9</f>
         <v>19.200000000000006</v>
       </c>
-      <c r="S121" s="3">
-        <f t="shared" ref="S121:S124" si="40">S120-0.8</f>
+      <c r="T121" s="3">
+        <f t="shared" ref="T121:T124" si="40">T120-0.8</f>
         <v>17.500000000000004</v>
       </c>
     </row>
-    <row r="122" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>20</v>
       </c>
@@ -5807,24 +5833,24 @@
       <c r="H122" s="2">
         <v>0.5</v>
       </c>
-      <c r="P122" s="3">
+      <c r="Q122" s="3">
         <f t="shared" si="19"/>
         <v>19.200000000000006</v>
       </c>
-      <c r="Q122" s="3">
+      <c r="R122" s="3">
         <f t="shared" si="20"/>
         <v>17.500000000000004</v>
       </c>
-      <c r="R122" s="3">
-        <f t="shared" ref="R122:R124" si="41">R121-0.9</f>
+      <c r="S122" s="3">
+        <f t="shared" ref="S122:S124" si="41">S121-0.9</f>
         <v>18.300000000000008</v>
       </c>
-      <c r="S122" s="3">
+      <c r="T122" s="3">
         <f t="shared" si="40"/>
         <v>16.700000000000003</v>
       </c>
     </row>
-    <row r="123" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>20</v>
       </c>
@@ -5846,24 +5872,24 @@
       <c r="H123" s="2">
         <v>0.5</v>
       </c>
-      <c r="P123" s="3">
+      <c r="Q123" s="3">
         <f t="shared" si="19"/>
         <v>18.300000000000008</v>
       </c>
-      <c r="Q123" s="3">
+      <c r="R123" s="3">
         <f t="shared" si="20"/>
         <v>16.700000000000003</v>
       </c>
-      <c r="R123" s="3">
+      <c r="S123" s="3">
         <f t="shared" si="41"/>
         <v>17.400000000000009</v>
       </c>
-      <c r="S123" s="3">
+      <c r="T123" s="3">
         <f t="shared" si="40"/>
         <v>15.900000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>20</v>
       </c>
@@ -5885,24 +5911,24 @@
       <c r="H124" s="2">
         <v>0.5</v>
       </c>
-      <c r="P124" s="3">
+      <c r="Q124" s="3">
         <f t="shared" si="19"/>
         <v>17.400000000000009</v>
       </c>
-      <c r="Q124" s="3">
+      <c r="R124" s="3">
         <f t="shared" si="20"/>
         <v>15.900000000000002</v>
       </c>
-      <c r="R124" s="3">
+      <c r="S124" s="3">
         <f t="shared" si="41"/>
         <v>16.500000000000011</v>
       </c>
-      <c r="S124" s="3">
+      <c r="T124" s="3">
         <f t="shared" si="40"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>20</v>
       </c>
@@ -5930,24 +5956,24 @@
       <c r="L125" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="P125" s="3">
+      <c r="Q125" s="3">
         <f t="shared" si="19"/>
         <v>16.500000000000011</v>
       </c>
-      <c r="Q125" s="3">
+      <c r="R125" s="3">
         <f t="shared" si="20"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R125" s="3">
-        <f>R124-0.5</f>
+      <c r="S125" s="3">
+        <f>S124-0.5</f>
         <v>16.000000000000011</v>
       </c>
-      <c r="S125" s="3">
-        <f>S124</f>
+      <c r="T125" s="3">
+        <f>T124</f>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>20</v>
       </c>
@@ -5978,24 +6004,24 @@
       <c r="N126" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="P126" s="3">
+      <c r="Q126" s="3">
         <f t="shared" si="19"/>
         <v>16.000000000000011</v>
       </c>
-      <c r="Q126" s="3">
+      <c r="R126" s="3">
         <f t="shared" si="20"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R126" s="3">
-        <f t="shared" ref="R126:R146" si="42">R125-0.5</f>
+      <c r="S126" s="3">
+        <f t="shared" ref="S126:S146" si="42">S125-0.5</f>
         <v>15.500000000000011</v>
       </c>
-      <c r="S126" s="3">
-        <f t="shared" ref="S126:S146" si="43">S125</f>
+      <c r="T126" s="3">
+        <f t="shared" ref="T126:T146" si="43">T125</f>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="127" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>20</v>
       </c>
@@ -6023,24 +6049,24 @@
       <c r="L127" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="P127" s="3">
+      <c r="Q127" s="3">
         <f t="shared" si="19"/>
         <v>15.500000000000011</v>
       </c>
-      <c r="Q127" s="3">
+      <c r="R127" s="3">
         <f t="shared" si="20"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R127" s="3">
+      <c r="S127" s="3">
         <f t="shared" si="42"/>
         <v>15.000000000000011</v>
       </c>
-      <c r="S127" s="3">
+      <c r="T127" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="128" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>20</v>
       </c>
@@ -6065,24 +6091,24 @@
       <c r="I128" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P128" s="3">
+      <c r="Q128" s="3">
         <f t="shared" si="19"/>
         <v>15.000000000000011</v>
       </c>
-      <c r="Q128" s="3">
+      <c r="R128" s="3">
         <f t="shared" si="20"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R128" s="3">
+      <c r="S128" s="3">
         <f t="shared" si="42"/>
         <v>14.500000000000011</v>
       </c>
-      <c r="S128" s="3">
+      <c r="T128" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="129" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>20</v>
       </c>
@@ -6107,24 +6133,24 @@
       <c r="I129" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P129" s="3">
+      <c r="Q129" s="3">
         <f t="shared" si="19"/>
         <v>14.500000000000011</v>
       </c>
-      <c r="Q129" s="3">
+      <c r="R129" s="3">
         <f t="shared" si="20"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R129" s="3">
+      <c r="S129" s="3">
         <f t="shared" si="42"/>
         <v>14.000000000000011</v>
       </c>
-      <c r="S129" s="3">
+      <c r="T129" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>20</v>
       </c>
@@ -6149,24 +6175,24 @@
       <c r="I130" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P130" s="3">
+      <c r="Q130" s="3">
         <f t="shared" si="19"/>
         <v>14.000000000000011</v>
       </c>
-      <c r="Q130" s="3">
+      <c r="R130" s="3">
         <f t="shared" si="20"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R130" s="3">
+      <c r="S130" s="3">
         <f t="shared" si="42"/>
         <v>13.500000000000011</v>
       </c>
-      <c r="S130" s="3">
+      <c r="T130" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>20</v>
       </c>
@@ -6191,24 +6217,24 @@
       <c r="I131" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P131" s="3">
-        <f t="shared" ref="P131:P153" si="44">R130</f>
+      <c r="Q131" s="3">
+        <f t="shared" ref="Q131:Q153" si="44">S130</f>
         <v>13.500000000000011</v>
       </c>
-      <c r="Q131" s="3">
-        <f t="shared" ref="Q131:Q153" si="45">S130</f>
+      <c r="R131" s="3">
+        <f t="shared" ref="R131:R153" si="45">T130</f>
         <v>15.100000000000001</v>
       </c>
-      <c r="R131" s="3">
+      <c r="S131" s="3">
         <f t="shared" si="42"/>
         <v>13.000000000000011</v>
       </c>
-      <c r="S131" s="3">
+      <c r="T131" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="132" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>20</v>
       </c>
@@ -6233,24 +6259,24 @@
       <c r="I132" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P132" s="3">
+      <c r="Q132" s="3">
         <f t="shared" si="44"/>
         <v>13.000000000000011</v>
       </c>
-      <c r="Q132" s="3">
+      <c r="R132" s="3">
         <f t="shared" si="45"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R132" s="3">
+      <c r="S132" s="3">
         <f t="shared" si="42"/>
         <v>12.500000000000011</v>
       </c>
-      <c r="S132" s="3">
+      <c r="T132" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="133" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>20</v>
       </c>
@@ -6275,24 +6301,24 @@
       <c r="I133" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P133" s="3">
+      <c r="Q133" s="3">
         <f t="shared" si="44"/>
         <v>12.500000000000011</v>
       </c>
-      <c r="Q133" s="3">
+      <c r="R133" s="3">
         <f t="shared" si="45"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R133" s="3">
+      <c r="S133" s="3">
         <f t="shared" si="42"/>
         <v>12.000000000000011</v>
       </c>
-      <c r="S133" s="3">
+      <c r="T133" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="134" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>20</v>
       </c>
@@ -6320,24 +6346,24 @@
       <c r="L134" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="P134" s="3">
+      <c r="Q134" s="3">
         <f t="shared" si="44"/>
         <v>12.000000000000011</v>
       </c>
-      <c r="Q134" s="3">
+      <c r="R134" s="3">
         <f t="shared" si="45"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R134" s="3">
+      <c r="S134" s="3">
         <f t="shared" si="42"/>
         <v>11.500000000000011</v>
       </c>
-      <c r="S134" s="3">
+      <c r="T134" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="135" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>20</v>
       </c>
@@ -6368,24 +6394,24 @@
       <c r="N135" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="P135" s="3">
+      <c r="Q135" s="3">
         <f t="shared" si="44"/>
         <v>11.500000000000011</v>
       </c>
-      <c r="Q135" s="3">
+      <c r="R135" s="3">
         <f t="shared" si="45"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R135" s="3">
+      <c r="S135" s="3">
         <f t="shared" si="42"/>
         <v>11.000000000000011</v>
       </c>
-      <c r="S135" s="3">
+      <c r="T135" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="136" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>20</v>
       </c>
@@ -6413,24 +6439,24 @@
       <c r="L136" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="P136" s="3">
+      <c r="Q136" s="3">
         <f t="shared" si="44"/>
         <v>11.000000000000011</v>
       </c>
-      <c r="Q136" s="3">
+      <c r="R136" s="3">
         <f t="shared" si="45"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R136" s="3">
+      <c r="S136" s="3">
         <f t="shared" si="42"/>
         <v>10.500000000000011</v>
       </c>
-      <c r="S136" s="3">
+      <c r="T136" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="137" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>20</v>
       </c>
@@ -6455,24 +6481,24 @@
       <c r="I137" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P137" s="3">
+      <c r="Q137" s="3">
         <f t="shared" si="44"/>
         <v>10.500000000000011</v>
       </c>
-      <c r="Q137" s="3">
+      <c r="R137" s="3">
         <f t="shared" si="45"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R137" s="3">
+      <c r="S137" s="3">
         <f t="shared" si="42"/>
         <v>10.000000000000011</v>
       </c>
-      <c r="S137" s="3">
+      <c r="T137" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="138" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>20</v>
       </c>
@@ -6497,24 +6523,24 @@
       <c r="I138" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P138" s="3">
+      <c r="Q138" s="3">
         <f t="shared" si="44"/>
         <v>10.000000000000011</v>
       </c>
-      <c r="Q138" s="3">
+      <c r="R138" s="3">
         <f t="shared" si="45"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R138" s="3">
+      <c r="S138" s="3">
         <f t="shared" si="42"/>
         <v>9.5000000000000107</v>
       </c>
-      <c r="S138" s="3">
+      <c r="T138" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="139" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>20</v>
       </c>
@@ -6539,24 +6565,24 @@
       <c r="I139" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P139" s="3">
+      <c r="Q139" s="3">
         <f t="shared" si="44"/>
         <v>9.5000000000000107</v>
       </c>
-      <c r="Q139" s="3">
+      <c r="R139" s="3">
         <f t="shared" si="45"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R139" s="3">
+      <c r="S139" s="3">
         <f t="shared" si="42"/>
         <v>9.0000000000000107</v>
       </c>
-      <c r="S139" s="3">
+      <c r="T139" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="140" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>20</v>
       </c>
@@ -6581,24 +6607,24 @@
       <c r="I140" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P140" s="3">
+      <c r="Q140" s="3">
         <f t="shared" si="44"/>
         <v>9.0000000000000107</v>
       </c>
-      <c r="Q140" s="3">
+      <c r="R140" s="3">
         <f t="shared" si="45"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R140" s="3">
+      <c r="S140" s="3">
         <f t="shared" si="42"/>
         <v>8.5000000000000107</v>
       </c>
-      <c r="S140" s="3">
+      <c r="T140" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="141" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>20</v>
       </c>
@@ -6623,24 +6649,24 @@
       <c r="I141" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P141" s="3">
+      <c r="Q141" s="3">
         <f t="shared" si="44"/>
         <v>8.5000000000000107</v>
       </c>
-      <c r="Q141" s="3">
+      <c r="R141" s="3">
         <f t="shared" si="45"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R141" s="3">
+      <c r="S141" s="3">
         <f t="shared" si="42"/>
         <v>8.0000000000000107</v>
       </c>
-      <c r="S141" s="3">
+      <c r="T141" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="142" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>20</v>
       </c>
@@ -6665,24 +6691,24 @@
       <c r="I142" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P142" s="3">
+      <c r="Q142" s="3">
         <f t="shared" si="44"/>
         <v>8.0000000000000107</v>
       </c>
-      <c r="Q142" s="3">
+      <c r="R142" s="3">
         <f t="shared" si="45"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R142" s="3">
+      <c r="S142" s="3">
         <f t="shared" si="42"/>
         <v>7.5000000000000107</v>
       </c>
-      <c r="S142" s="3">
+      <c r="T142" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>20</v>
       </c>
@@ -6710,24 +6736,24 @@
       <c r="L143" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="P143" s="3">
+      <c r="Q143" s="3">
         <f t="shared" si="44"/>
         <v>7.5000000000000107</v>
       </c>
-      <c r="Q143" s="3">
+      <c r="R143" s="3">
         <f t="shared" si="45"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R143" s="3">
+      <c r="S143" s="3">
         <f t="shared" si="42"/>
         <v>7.0000000000000107</v>
       </c>
-      <c r="S143" s="3">
+      <c r="T143" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="144" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>20</v>
       </c>
@@ -6758,24 +6784,24 @@
       <c r="N144" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="P144" s="3">
+      <c r="Q144" s="3">
         <f t="shared" si="44"/>
         <v>7.0000000000000107</v>
       </c>
-      <c r="Q144" s="3">
+      <c r="R144" s="3">
         <f t="shared" si="45"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R144" s="3">
+      <c r="S144" s="3">
         <f t="shared" si="42"/>
         <v>6.5000000000000107</v>
       </c>
-      <c r="S144" s="3">
+      <c r="T144" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="145" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>20</v>
       </c>
@@ -6803,24 +6829,24 @@
       <c r="L145" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="P145" s="3">
+      <c r="Q145" s="3">
         <f t="shared" si="44"/>
         <v>6.5000000000000107</v>
       </c>
-      <c r="Q145" s="3">
+      <c r="R145" s="3">
         <f t="shared" si="45"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R145" s="3">
+      <c r="S145" s="3">
         <f t="shared" si="42"/>
         <v>6.0000000000000107</v>
       </c>
-      <c r="S145" s="3">
+      <c r="T145" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="146" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>20</v>
       </c>
@@ -6845,24 +6871,24 @@
       <c r="I146" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P146" s="3">
+      <c r="Q146" s="3">
         <f t="shared" si="44"/>
         <v>6.0000000000000107</v>
       </c>
-      <c r="Q146" s="3">
+      <c r="R146" s="3">
         <f t="shared" si="45"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R146" s="3">
+      <c r="S146" s="3">
         <f t="shared" si="42"/>
         <v>5.5000000000000107</v>
       </c>
-      <c r="S146" s="3">
+      <c r="T146" s="3">
         <f t="shared" si="43"/>
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="147" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>20</v>
       </c>
@@ -6884,24 +6910,24 @@
       <c r="H147" s="2">
         <v>0.5</v>
       </c>
-      <c r="P147" s="3">
+      <c r="Q147" s="3">
         <f t="shared" si="44"/>
         <v>5.5000000000000107</v>
       </c>
-      <c r="Q147" s="3">
+      <c r="R147" s="3">
         <f t="shared" si="45"/>
         <v>15.100000000000001</v>
       </c>
-      <c r="R147" s="3">
-        <f>R146-0.8</f>
+      <c r="S147" s="3">
+        <f>S146-0.8</f>
         <v>4.7000000000000108</v>
       </c>
-      <c r="S147" s="3">
-        <f>S146-0.7</f>
+      <c r="T147" s="3">
+        <f>T146-0.7</f>
         <v>14.400000000000002</v>
       </c>
     </row>
-    <row r="148" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>20</v>
       </c>
@@ -6923,24 +6949,24 @@
       <c r="H148" s="2">
         <v>0.5</v>
       </c>
-      <c r="P148" s="3">
+      <c r="Q148" s="3">
         <f t="shared" si="44"/>
         <v>4.7000000000000108</v>
       </c>
-      <c r="Q148" s="3">
+      <c r="R148" s="3">
         <f t="shared" si="45"/>
         <v>14.400000000000002</v>
       </c>
-      <c r="R148" s="3">
-        <f t="shared" ref="R148:R149" si="46">R147-0.8</f>
+      <c r="S148" s="3">
+        <f t="shared" ref="S148:S149" si="46">S147-0.8</f>
         <v>3.900000000000011</v>
       </c>
-      <c r="S148" s="3">
-        <f t="shared" ref="S148:S149" si="47">S147-0.7</f>
+      <c r="T148" s="3">
+        <f t="shared" ref="T148:T149" si="47">T147-0.7</f>
         <v>13.700000000000003</v>
       </c>
     </row>
-    <row r="149" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>20</v>
       </c>
@@ -6962,24 +6988,24 @@
       <c r="H149" s="2">
         <v>0.5</v>
       </c>
-      <c r="P149" s="3">
+      <c r="Q149" s="3">
         <f t="shared" si="44"/>
         <v>3.900000000000011</v>
       </c>
-      <c r="Q149" s="3">
+      <c r="R149" s="3">
         <f t="shared" si="45"/>
         <v>13.700000000000003</v>
       </c>
-      <c r="R149" s="3">
+      <c r="S149" s="3">
         <f t="shared" si="46"/>
         <v>3.1000000000000112</v>
       </c>
-      <c r="S149" s="3">
+      <c r="T149" s="3">
         <f t="shared" si="47"/>
         <v>13.000000000000004</v>
       </c>
     </row>
-    <row r="150" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>20</v>
       </c>
@@ -7001,24 +7027,24 @@
       <c r="H150" s="2">
         <v>0.5</v>
       </c>
-      <c r="P150" s="3">
+      <c r="Q150" s="3">
         <f t="shared" si="44"/>
         <v>3.1000000000000112</v>
       </c>
-      <c r="Q150" s="3">
+      <c r="R150" s="3">
         <f t="shared" si="45"/>
         <v>13.000000000000004</v>
       </c>
-      <c r="R150" s="3">
-        <f>R149</f>
+      <c r="S150" s="3">
+        <f>S149</f>
         <v>3.1000000000000112</v>
       </c>
-      <c r="S150" s="3">
-        <f>S149-0.8</f>
+      <c r="T150" s="3">
+        <f>T149-0.8</f>
         <v>12.200000000000003</v>
       </c>
     </row>
-    <row r="151" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>20</v>
       </c>
@@ -7040,24 +7066,24 @@
       <c r="H151" s="2">
         <v>0.5</v>
       </c>
-      <c r="P151" s="3">
+      <c r="Q151" s="3">
         <f t="shared" si="44"/>
         <v>3.1000000000000112</v>
       </c>
-      <c r="Q151" s="3">
+      <c r="R151" s="3">
         <f t="shared" si="45"/>
         <v>12.200000000000003</v>
       </c>
-      <c r="R151" s="3">
-        <f t="shared" ref="R151:R152" si="48">R150</f>
+      <c r="S151" s="3">
+        <f t="shared" ref="S151:S152" si="48">S150</f>
         <v>3.1000000000000112</v>
       </c>
-      <c r="S151" s="3">
-        <f t="shared" ref="S151:S152" si="49">S150-0.8</f>
+      <c r="T151" s="3">
+        <f t="shared" ref="T151:T152" si="49">T150-0.8</f>
         <v>11.400000000000002</v>
       </c>
     </row>
-    <row r="152" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>20</v>
       </c>
@@ -7079,24 +7105,24 @@
       <c r="H152" s="2">
         <v>0.5</v>
       </c>
-      <c r="P152" s="3">
+      <c r="Q152" s="3">
         <f t="shared" si="44"/>
         <v>3.1000000000000112</v>
       </c>
-      <c r="Q152" s="3">
+      <c r="R152" s="3">
         <f t="shared" si="45"/>
         <v>11.400000000000002</v>
       </c>
-      <c r="R152" s="3">
+      <c r="S152" s="3">
         <f t="shared" si="48"/>
         <v>3.1000000000000112</v>
       </c>
-      <c r="S152" s="3">
+      <c r="T152" s="3">
         <f t="shared" si="49"/>
         <v>10.600000000000001</v>
       </c>
     </row>
-    <row r="153" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>20</v>
       </c>
@@ -7118,25 +7144,25 @@
       <c r="H153" s="2">
         <v>0.5</v>
       </c>
-      <c r="P153" s="3">
+      <c r="Q153" s="3">
         <f t="shared" si="44"/>
         <v>3.1000000000000112</v>
       </c>
-      <c r="Q153" s="3">
+      <c r="R153" s="3">
         <f t="shared" si="45"/>
         <v>10.600000000000001</v>
       </c>
-      <c r="R153" s="3">
+      <c r="S153" s="3">
         <v>4.5</v>
       </c>
-      <c r="S153" s="3">
+      <c r="T153" s="3">
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H155"/>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H156"/>
     </row>
   </sheetData>

--- a/TrackModel/Green Line.xlsx
+++ b/TrackModel/Green Line.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pitt-my.sharepoint.com/personal/dgs44_pitt_edu/Documents/Trains/TrackModel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="692" documentId="8_{D0660D75-C052-4898-8402-12AA78E71664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{214EED10-7E9C-414B-B0E9-593AE83C0A2A}"/>
+  <xr:revisionPtr revIDLastSave="696" documentId="8_{D0660D75-C052-4898-8402-12AA78E71664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B73CDC8-A020-4430-AF3D-A382C8078181}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{C71A2FFE-490E-4D57-BAA4-DE7AC575C897}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C71A2FFE-490E-4D57-BAA4-DE7AC575C897}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="77">
   <si>
     <t>A</t>
   </si>
@@ -3956,9 +3956,6 @@
       <c r="F77" s="2">
         <v>40</v>
       </c>
-      <c r="G77" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H77" s="2">
         <v>0.5</v>
       </c>
@@ -4001,9 +3998,6 @@
       <c r="F78" s="2">
         <v>40</v>
       </c>
-      <c r="G78" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H78" s="2">
         <v>0.5</v>
       </c>
@@ -4043,9 +4037,6 @@
       <c r="F79" s="2">
         <v>40</v>
       </c>
-      <c r="G79" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H79" s="2">
         <v>0.5</v>
       </c>
@@ -4493,9 +4484,6 @@
       <c r="F89" s="2">
         <v>25</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H89" s="2">
         <v>0.5</v>
       </c>
@@ -4535,9 +4523,6 @@
       <c r="F90" s="2">
         <v>25</v>
       </c>
-      <c r="G90" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H90" s="2">
         <v>0.5</v>
       </c>
@@ -4579,9 +4564,6 @@
       </c>
       <c r="F91" s="2">
         <v>25</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="H91" s="2">
         <v>0.5</v>
